--- a/data/catalog/switching.xlsx
+++ b/data/catalog/switching.xlsx
@@ -1037,3268 +1037,3268 @@
     <t>https://documentation.meraki.com/Switching/MS_-_Switches/Install_and_Get_Started/Installation_Guides/MS150_Series_Installation_Guide</t>
   </si>
   <si>
+    <t>switching.csv row 14</t>
+  </si>
+  <si>
+    <t>MS150: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>Fan</t>
+  </si>
+  <si>
+    <t>MS150-24P-4G</t>
+  </si>
+  <si>
+    <t>poe, fan</t>
+  </si>
+  <si>
+    <t>switching.csv row 15</t>
+  </si>
+  <si>
+    <t>MS150: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Fan</t>
+  </si>
+  <si>
+    <t>MS150-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 16</t>
+  </si>
+  <si>
+    <t>MS150: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-48LP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 17</t>
+  </si>
+  <si>
+    <t>MS150: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-48FP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 18</t>
+  </si>
+  <si>
+    <t>MS150-24T-4X</t>
+  </si>
+  <si>
     <t>switching.csv row 19</t>
   </si>
   <si>
-    <t>MS150: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>Fan</t>
-  </si>
-  <si>
-    <t>MS150-24P-4G</t>
-  </si>
-  <si>
-    <t>poe, fan</t>
+    <t>MS150: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-24P-4X</t>
   </si>
   <si>
     <t>switching.csv row 20</t>
   </si>
   <si>
-    <t>MS150: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Fan</t>
-  </si>
-  <si>
-    <t>MS150-48T-4G</t>
+    <t>MS150: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-48T-4X</t>
   </si>
   <si>
     <t>switching.csv row 21</t>
   </si>
   <si>
-    <t>MS150: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-48LP-4G</t>
+    <t>MS150: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-48LP-4X</t>
   </si>
   <si>
     <t>switching.csv row 22</t>
   </si>
   <si>
-    <t>MS150: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-48FP-4G</t>
+    <t>MS150: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS150-48FP-4X</t>
   </si>
   <si>
     <t>switching.csv row 23</t>
   </si>
   <si>
-    <t>MS150-24T-4X</t>
+    <t>MS150-24MP-4X</t>
+  </si>
+  <si>
+    <t>poe, multigigabit, fan</t>
   </si>
   <si>
     <t>switching.csv row 24</t>
   </si>
   <si>
-    <t>MS150: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-24P-4X</t>
+    <t>MS150: 24x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Multigigabit, Fan</t>
+  </si>
+  <si>
+    <t>MS150-48MP-4X</t>
   </si>
   <si>
     <t>switching.csv row 25</t>
   </si>
   <si>
-    <t>MS150: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-48T-4X</t>
+    <t>MS150: 48x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS210-24-HW</t>
+  </si>
+  <si>
+    <t>MS210</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2031-04-30</t>
+  </si>
+  <si>
+    <t>MS130 / MS150 | confirm per model</t>
+  </si>
+  <si>
+    <t>https://documentation.meraki.com/General_Administration/Other_Topics/Product_End-of-Life_(EOL)_Policies</t>
+  </si>
+  <si>
+    <t>https://documentation.meraki.com/Switching/MS_-_Switches/Product_Information/Overviews_and_Datasheets/MS210_Overview_and_Specifications</t>
+  </si>
+  <si>
+    <t>stacking, fan</t>
   </si>
   <si>
     <t>switching.csv row 26</t>
   </si>
   <si>
-    <t>MS150: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-48LP-4X</t>
+    <t>MS210: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>Stacking, Fan</t>
+  </si>
+  <si>
+    <t>MS210-24P-HW</t>
+  </si>
+  <si>
+    <t>poe, stacking, fan</t>
   </si>
   <si>
     <t>switching.csv row 27</t>
   </si>
   <si>
-    <t>MS150: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS150-48FP-4X</t>
+    <t>MS210: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Fan</t>
+  </si>
+  <si>
+    <t>MS210-48-HW</t>
   </si>
   <si>
     <t>switching.csv row 28</t>
   </si>
   <si>
-    <t>MS150-24MP-4X</t>
-  </si>
-  <si>
-    <t>poe, multigigabit, fan</t>
+    <t>MS210: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS210-48LP-HW</t>
   </si>
   <si>
     <t>switching.csv row 29</t>
   </si>
   <si>
-    <t>MS150: 24x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Multigigabit, Fan</t>
-  </si>
-  <si>
-    <t>MS150-48MP-4X</t>
+    <t>MS210: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>MS210-48FP-HW</t>
   </si>
   <si>
     <t>switching.csv row 30</t>
   </si>
   <si>
-    <t>MS150: 48x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS210-24-HW</t>
-  </si>
-  <si>
-    <t>MS210</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2031-04-30</t>
-  </si>
-  <si>
-    <t>MS130 / MS150 | confirm per model</t>
-  </si>
-  <si>
-    <t>https://documentation.meraki.com/General_Administration/Other_Topics/Product_End-of-Life_(EOL)_Policies</t>
-  </si>
-  <si>
-    <t>https://documentation.meraki.com/Switching/MS_-_Switches/Product_Information/Overviews_and_Datasheets/MS210_Overview_and_Specifications</t>
-  </si>
-  <si>
-    <t>stacking, fan</t>
+    <t>MS450-12-HW</t>
+  </si>
+  <si>
+    <t>MS450</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>2031-10-31</t>
+  </si>
+  <si>
+    <t>C9500-32QC</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/networking/switches/meraki-switches/meraki-ms450-12x40g-aggregation-switch-eol.html</t>
+  </si>
+  <si>
+    <t>https://documentation.meraki.com/Switching/MS_-_Switches/Install_and_Get_Started/Installation_Guides/MS450_Series_Installation_Guide</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>stacking, redundant_psu, fan</t>
   </si>
   <si>
     <t>switching.csv row 31</t>
   </si>
   <si>
-    <t>MS210: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>Stacking, Fan</t>
-  </si>
-  <si>
-    <t>MS210-24P-HW</t>
-  </si>
-  <si>
-    <t>poe, stacking, fan</t>
+    <t>MS450: 12x 40G Fiber downlinks and 2x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>Stacking, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9200L-24T-4X-M</t>
+  </si>
+  <si>
+    <t>9200L-M</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9200-series-switches/datasheet-listing.html</t>
   </si>
   <si>
     <t>switching.csv row 32</t>
   </si>
   <si>
-    <t>MS210: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Fan</t>
-  </si>
-  <si>
-    <t>MS210-48-HW</t>
+    <t>9200L-M: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>Meraki Switches: Add powercord separately (ma-pwr-cord-eu)! No support for BGP, PTP, MACSEC-256 on 9200/9200L series</t>
+  </si>
+  <si>
+    <t>C9200L-48T-4X-M</t>
   </si>
   <si>
     <t>switching.csv row 33</t>
   </si>
   <si>
-    <t>MS210: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS210-48LP-HW</t>
+    <t>9200L-M: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24T-4G-M</t>
   </si>
   <si>
     <t>switching.csv row 34</t>
   </si>
   <si>
-    <t>MS210: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>MS210-48FP-HW</t>
+    <t>9200L-M: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48T-4G-M</t>
   </si>
   <si>
     <t>switching.csv row 35</t>
   </si>
   <si>
-    <t>MS450-12-HW</t>
-  </si>
-  <si>
-    <t>MS450</t>
-  </si>
-  <si>
-    <t>2026-10-29</t>
-  </si>
-  <si>
-    <t>2031-10-31</t>
-  </si>
-  <si>
-    <t>C9500-32QC</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/networking/switches/meraki-switches/meraki-ms450-12x40g-aggregation-switch-eol.html</t>
-  </si>
-  <si>
-    <t>https://documentation.meraki.com/Switching/MS_-_Switches/Install_and_Get_Started/Installation_Guides/MS450_Series_Installation_Guide</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>stacking, redundant_psu, fan</t>
+    <t>9200L-M: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24P-4X-M</t>
+  </si>
+  <si>
+    <t>poe, stacking, redundant_psu, fan</t>
   </si>
   <si>
     <t>switching.csv row 36</t>
   </si>
   <si>
-    <t>MS450: 12x 40G Fiber downlinks and 2x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>Stacking, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9200L-24T-4X-M</t>
-  </si>
-  <si>
-    <t>9200L-M</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9200-series-switches/datasheet-listing.html</t>
+    <t>9200L-M: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9200L-24P-4G-M</t>
   </si>
   <si>
     <t>switching.csv row 37</t>
   </si>
   <si>
-    <t>9200L-M: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>Meraki Switches: Add powercord separately (ma-pwr-cord-eu)! No support for BGP, PTP, MACSEC-256 on 9200/9200L series</t>
-  </si>
-  <si>
-    <t>C9200L-48T-4X-M</t>
+    <t>9200L-M: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PL-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 38</t>
+  </si>
+  <si>
+    <t>9200L-M: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48P-4X-M</t>
   </si>
   <si>
     <t>switching.csv row 39</t>
   </si>
   <si>
-    <t>9200L-M: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24T-4G-M</t>
+    <t>C9200L-48P-4G-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 40</t>
+  </si>
+  <si>
+    <t>9200L-M: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PL-4G-M</t>
   </si>
   <si>
     <t>switching.csv row 41</t>
   </si>
   <si>
-    <t>9200L-M: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48T-4G-M</t>
+    <t>C9200L-24PXG-4X-M</t>
+  </si>
+  <si>
+    <t>poe, stacking, multigigabit, redundant_psu, fan</t>
+  </si>
+  <si>
+    <t>switching.csv row 42</t>
+  </si>
+  <si>
+    <t>9200L-M:24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Multigigabit, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9200L-24PXG-2Y-M</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>switching.csv row 43</t>
   </si>
   <si>
-    <t>9200L-M: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24P-4X-M</t>
-  </si>
-  <si>
-    <t>poe, stacking, redundant_psu, fan</t>
+    <t>9200L-M: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PXG-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 44</t>
+  </si>
+  <si>
+    <t>9200L-M: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PXG-2Y-M</t>
   </si>
   <si>
     <t>switching.csv row 45</t>
   </si>
   <si>
-    <t>9200L-M: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9200L-24P-4G-M</t>
+    <t>9200L-M: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24T-M</t>
+  </si>
+  <si>
+    <t>9300-M</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9300-series-switches/datasheet-listing.html</t>
+  </si>
+  <si>
+    <t>1, 10, 25, 40</t>
+  </si>
+  <si>
+    <t>stacking, stackpower, redundant_psu, fan</t>
+  </si>
+  <si>
+    <t>switching.csv row 46</t>
+  </si>
+  <si>
+    <t>9300-M: 24x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>Meraki Switches: Add powercord separately (ma-pwr-cord-eu)!</t>
+  </si>
+  <si>
+    <t>Stacking, StackPower, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9300-24P-M</t>
+  </si>
+  <si>
+    <t>poe, stacking, stackpower, redundant_psu, fan</t>
   </si>
   <si>
     <t>switching.csv row 47</t>
   </si>
   <si>
-    <t>9200L-M: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PL-4X-M</t>
+    <t>9300-M: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, StackPower, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9300-24U-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 48</t>
+  </si>
+  <si>
+    <t>9300-M: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48T-M</t>
   </si>
   <si>
     <t>switching.csv row 49</t>
   </si>
   <si>
-    <t>9200L-M: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48P-4X-M</t>
+    <t>9300-M: 48x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48P-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 50</t>
+  </si>
+  <si>
+    <t>9300-M: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48U-M</t>
   </si>
   <si>
     <t>switching.csv row 51</t>
   </si>
   <si>
-    <t>C9200L-48P-4G-M</t>
+    <t>9300-M: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24UX-M</t>
+  </si>
+  <si>
+    <t>poe, stacking, multigigabit, stackpower, redundant_psu, fan</t>
+  </si>
+  <si>
+    <t>switching.csv row 52</t>
+  </si>
+  <si>
+    <t>9300-M: 24x UPOE 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Multigigabit, StackPower, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9300-48UXM-M</t>
   </si>
   <si>
     <t>switching.csv row 53</t>
   </si>
   <si>
-    <t>9200L-M: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PL-4G-M</t>
+    <t>9300-M: 48x UPOE 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48UN-M</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>switching.csv row 54</t>
+  </si>
+  <si>
+    <t>9300-M: 48x UPOE 5G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24S-M</t>
   </si>
   <si>
     <t>switching.csv row 55</t>
   </si>
   <si>
-    <t>C9200L-24PXG-4X-M</t>
-  </si>
-  <si>
-    <t>poe, stacking, multigigabit, redundant_psu, fan</t>
+    <t>9300-M: 24x 1G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48S-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 56</t>
+  </si>
+  <si>
+    <t>9300-M: 48x 1G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24T-4X-M</t>
+  </si>
+  <si>
+    <t>9300L-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 63</t>
+  </si>
+  <si>
+    <t>9300L-M: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48T-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 64</t>
+  </si>
+  <si>
+    <t>9300L-M: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24P-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 65</t>
+  </si>
+  <si>
+    <t>9300L-M: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48P-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 66</t>
+  </si>
+  <si>
+    <t>9300L-M: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48PF-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 67</t>
+  </si>
+  <si>
+    <t>C9300L-24UXG-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 68</t>
+  </si>
+  <si>
+    <t>9300L-M: 24x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48UXG-4X-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 69</t>
+  </si>
+  <si>
+    <t>9300L-M: 48x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48TX-M</t>
+  </si>
+  <si>
+    <t>9300X-M</t>
+  </si>
+  <si>
+    <t>10, 25, 100</t>
+  </si>
+  <si>
+    <t>stacking, multigigabit, stackpower, redundant_psu, fan</t>
+  </si>
+  <si>
+    <t>switching.csv row 70</t>
+  </si>
+  <si>
+    <t>9300X-M: 48x 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>Stacking, Multigigabit, StackPower, Redundant PSU, Fan</t>
+  </si>
+  <si>
+    <t>C9300X-24HX-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 71</t>
+  </si>
+  <si>
+    <t>9300X-M: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48HX-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 72</t>
+  </si>
+  <si>
+    <t>9300X-M: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48HXN-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 73</t>
+  </si>
+  <si>
+    <t>9300X-M: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-12Y-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 74</t>
+  </si>
+  <si>
+    <t>9300X-M: 12x 25G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-24Y-M</t>
+  </si>
+  <si>
+    <t>switching.csv row 75</t>
+  </si>
+  <si>
+    <t>9300X-M: 24x 25G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C1200-8T-D</t>
+  </si>
+  <si>
+    <t>C1200</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-1200-series-switches/datasheet-listing.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 81</t>
+  </si>
+  <si>
+    <t>C1200: 8x 1G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C1200 series don't support stacking!</t>
+  </si>
+  <si>
+    <t>C1200-8T-E-2G</t>
+  </si>
+  <si>
+    <t>copper, fiber</t>
+  </si>
+  <si>
+    <t>switching.csv row 82</t>
+  </si>
+  <si>
+    <t>C1200: 8x 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-8P-E-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 83</t>
+  </si>
+  <si>
+    <t>C1200: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-8FP-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 84</t>
+  </si>
+  <si>
+    <t>C1200: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-16T-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 85</t>
+  </si>
+  <si>
+    <t>C1200: 16x 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-16P-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 86</t>
+  </si>
+  <si>
+    <t>C1200: 16x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 87</t>
+  </si>
+  <si>
+    <t>C1200: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 88</t>
+  </si>
+  <si>
+    <t>C1200: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24FP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 89</t>
+  </si>
+  <si>
+    <t>C1200-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 90</t>
+  </si>
+  <si>
+    <t>C1200: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-48P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 91</t>
+  </si>
+  <si>
+    <t>C1200: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 92</t>
+  </si>
+  <si>
+    <t>C1200: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 93</t>
+  </si>
+  <si>
+    <t>C1200: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-24FP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 94</t>
+  </si>
+  <si>
+    <t>C1200-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 95</t>
+  </si>
+  <si>
+    <t>C1200: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1200-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 96</t>
+  </si>
+  <si>
+    <t>C1200: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-8T-E-2G</t>
+  </si>
+  <si>
+    <t>C1300</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-1200-series-switches/nb-06-cat1200-1300-ser-aag-cte-en.pdf</t>
+  </si>
+  <si>
+    <t>switching.csv row 97</t>
+  </si>
+  <si>
+    <t>C1300: 8x 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300 series with 1G uplinks can't stack</t>
+  </si>
+  <si>
+    <t>C1300-8P-E-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 98</t>
+  </si>
+  <si>
+    <t>C1300: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-8FP-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 99</t>
+  </si>
+  <si>
+    <t>C1300: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-16T-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 100</t>
+  </si>
+  <si>
+    <t>C1300: 16x 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-16P-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 101</t>
+  </si>
+  <si>
+    <t>C1300: 16x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-16FP-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 102</t>
+  </si>
+  <si>
+    <t>C1300-24T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 103</t>
+  </si>
+  <si>
+    <t>C1300: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-24P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 104</t>
+  </si>
+  <si>
+    <t>C1300: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-24FP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 105</t>
+  </si>
+  <si>
+    <t>PoE,SMB</t>
+  </si>
+  <si>
+    <t>C1300-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 106</t>
+  </si>
+  <si>
+    <t>C1300: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-48P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 107</t>
+  </si>
+  <si>
+    <t>C1300: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-48FP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 108</t>
+  </si>
+  <si>
+    <t>C1300-16P-4X</t>
+  </si>
+  <si>
+    <t>poe, stacking, fan, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 109</t>
+  </si>
+  <si>
+    <t>C1300: 16x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Fan, SMB</t>
+  </si>
+  <si>
+    <t>C1300-24T-4X</t>
+  </si>
+  <si>
+    <t>stacking, fan, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 110</t>
+  </si>
+  <si>
+    <t>C1300: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>Stacking, Fan, SMB</t>
+  </si>
+  <si>
+    <t>C1300-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 111</t>
+  </si>
+  <si>
+    <t>C1300: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-24FP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 112</t>
+  </si>
+  <si>
+    <t>C1300-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 113</t>
+  </si>
+  <si>
+    <t>C1300: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 114</t>
+  </si>
+  <si>
+    <t>C1300: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-48FP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 115</t>
+  </si>
+  <si>
+    <t>C1300-8MGP-2X</t>
+  </si>
+  <si>
+    <t>poe, stacking, multigigabit, fan, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 116</t>
+  </si>
+  <si>
+    <t>C1300: 8x PoE+ 2.5G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Stacking, Multigigabit, Fan, SMB</t>
+  </si>
+  <si>
+    <t>C1300-24MGP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 117</t>
+  </si>
+  <si>
+    <t>C1300: 24x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-48MGP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 118</t>
+  </si>
+  <si>
+    <t>C1300: 48x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-12XT-2X</t>
+  </si>
+  <si>
+    <t>switching.csv row 119</t>
+  </si>
+  <si>
+    <t>C1300: 12x 10G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300-12XS</t>
+  </si>
+  <si>
+    <t>switching.csv row 120</t>
+  </si>
+  <si>
+    <t>C1300: 12x 10G Copper/ Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C1300-16XTS</t>
+  </si>
+  <si>
+    <t>switching.csv row 121</t>
+  </si>
+  <si>
+    <t>C1300: 16x 10G Copper/ Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C1300-24XS</t>
+  </si>
+  <si>
+    <t>switching.csv row 122</t>
+  </si>
+  <si>
+    <t>C1300: 24x 10G Copper/ Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C1300-24XT</t>
+  </si>
+  <si>
+    <t>switching.csv row 123</t>
+  </si>
+  <si>
+    <t>C1300: 24x 10G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C1300-24XTS</t>
+  </si>
+  <si>
+    <t>switching.csv row 124</t>
+  </si>
+  <si>
+    <t>C1300: 24x 10G Hybrid downlinks</t>
+  </si>
+  <si>
+    <t>C1300X-24T-4X</t>
+  </si>
+  <si>
+    <t>C1300X</t>
+  </si>
+  <si>
+    <t>switching.csv row 125</t>
+  </si>
+  <si>
+    <t>C1300X: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 126</t>
+  </si>
+  <si>
+    <t>C1300X: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 127</t>
+  </si>
+  <si>
+    <t>C1300X: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 128</t>
+  </si>
+  <si>
+    <t>C1300X: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-24MU-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 129</t>
+  </si>
+  <si>
+    <t>C1300X: 24x UPOE 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-10NU-2X</t>
+  </si>
+  <si>
+    <t>switching.csv row 130</t>
+  </si>
+  <si>
+    <t>C1300X: 10x UPOE 5G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-24NGU-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 131</t>
+  </si>
+  <si>
+    <t>C1300X: 24x UPOE 5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C1300X-48NGU-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 132</t>
+  </si>
+  <si>
+    <t>C1300X: 48x UPOE 5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-24T</t>
+  </si>
+  <si>
+    <t>C9200</t>
+  </si>
+  <si>
+    <t>switching.csv row 133</t>
+  </si>
+  <si>
+    <t>C9200: 24x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>No support for BGP, PTP, MACSEC-256 on 9200/9200L series</t>
+  </si>
+  <si>
+    <t>C9200-24P</t>
+  </si>
+  <si>
+    <t>switching.csv row 134</t>
+  </si>
+  <si>
+    <t>C9200: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9200-24PB</t>
+  </si>
+  <si>
+    <t>switching.csv row 135</t>
+  </si>
+  <si>
+    <t>C9200-24PXG</t>
+  </si>
+  <si>
+    <t>switching.csv row 136</t>
+  </si>
+  <si>
+    <t>C9200: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9200-48T</t>
+  </si>
+  <si>
+    <t>switching.csv row 137</t>
+  </si>
+  <si>
+    <t>C9200: 48x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9200-48P</t>
+  </si>
+  <si>
+    <t>switching.csv row 138</t>
+  </si>
+  <si>
+    <t>C9200: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9200-48PL</t>
+  </si>
+  <si>
+    <t>switching.csv row 139</t>
+  </si>
+  <si>
+    <t>C9200-48PB</t>
+  </si>
+  <si>
+    <t>switching.csv row 140</t>
+  </si>
+  <si>
+    <t>C9200-48PXG</t>
+  </si>
+  <si>
+    <t>switching.csv row 141</t>
+  </si>
+  <si>
+    <t>C9200: 48 ports full PoE+ (8 mGig ports up to 10G, 40 ports up to 1G) and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24T-4G</t>
+  </si>
+  <si>
+    <t>C9200L</t>
+  </si>
+  <si>
+    <t>on_prem, cloud</t>
+  </si>
+  <si>
+    <t>switching.csv row 147</t>
+  </si>
+  <si>
+    <t>C9200L: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 148</t>
+  </si>
+  <si>
+    <t>C9200L: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 149</t>
+  </si>
+  <si>
+    <t>C9200L: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 150</t>
+  </si>
+  <si>
+    <t>C9200L: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PL-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 151</t>
+  </si>
+  <si>
+    <t>C9200L-24T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 152</t>
+  </si>
+  <si>
+    <t>C9200L: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 153</t>
+  </si>
+  <si>
+    <t>C9200L: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 154</t>
+  </si>
+  <si>
+    <t>C9200L: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 155</t>
+  </si>
+  <si>
+    <t>C9200L: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PL-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 156</t>
+  </si>
+  <si>
+    <t>C9200L-24PXG-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 157</t>
+  </si>
+  <si>
+    <t>C9200L: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PXG-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 158</t>
+  </si>
+  <si>
+    <t>C9200L: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-24PXG-2Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 159</t>
+  </si>
+  <si>
+    <t>C9200L: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200L-48PXG-2Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 160</t>
+  </si>
+  <si>
+    <t>C9200L: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200CX-12T-2X2G</t>
+  </si>
+  <si>
+    <t>C9200CX</t>
+  </si>
+  <si>
+    <t>1, 10</t>
+  </si>
+  <si>
+    <t>switching.csv row 161</t>
+  </si>
+  <si>
+    <t>C9200CX: 12x 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>No support for stacking!</t>
+  </si>
+  <si>
+    <t>C9200CX-12P-2X2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 162</t>
+  </si>
+  <si>
+    <t>C9200CX: 12x PoE+ 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE</t>
+  </si>
+  <si>
+    <t>C9200CX-8P-2X2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 163</t>
+  </si>
+  <si>
+    <t>C9200CX: 8x PoE+ 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200CX-8UXG-2X</t>
+  </si>
+  <si>
+    <t>poe, multigigabit</t>
+  </si>
+  <si>
+    <t>switching.csv row 164</t>
+  </si>
+  <si>
+    <t>C9200CX: 8 ports UPOE (4 mGig ports up to 10G, 4 ports up to 1G) and 2x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>PoE, Multigigabit</t>
+  </si>
+  <si>
+    <t>C9200CX-12P-2XGH</t>
+  </si>
+  <si>
+    <t>switching.csv row 165</t>
+  </si>
+  <si>
+    <t>C9200CX-8P-2XGH</t>
+  </si>
+  <si>
+    <t>switching.csv row 166</t>
+  </si>
+  <si>
+    <t>C9200CX-8UXG-2XH</t>
+  </si>
+  <si>
+    <t>switching.csv row 167</t>
+  </si>
+  <si>
+    <t>C9200CX:8 ports UPOE (4 mGig ports up to 10G, 4 ports up to 1G) and 2x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200CX-8PT-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 168</t>
+  </si>
+  <si>
+    <t>C9200CX: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24T</t>
+  </si>
+  <si>
+    <t>C9300</t>
+  </si>
+  <si>
+    <t>switching.csv row 169</t>
+  </si>
+  <si>
+    <t>C9300: 24x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24P</t>
+  </si>
+  <si>
+    <t>switching.csv row 170</t>
+  </si>
+  <si>
+    <t>C9300: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24U</t>
+  </si>
+  <si>
+    <t>switching.csv row 171</t>
+  </si>
+  <si>
+    <t>C9300: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24UB</t>
+  </si>
+  <si>
+    <t>switching.csv row 172</t>
+  </si>
+  <si>
+    <t>C9300-24H</t>
+  </si>
+  <si>
+    <t>switching.csv row 173</t>
+  </si>
+  <si>
+    <t>C9300: 24x UPOE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24UX</t>
+  </si>
+  <si>
+    <t>switching.csv row 174</t>
+  </si>
+  <si>
+    <t>C9300: 24x UPOE 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24UXB</t>
+  </si>
+  <si>
+    <t>switching.csv row 175</t>
+  </si>
+  <si>
+    <t>C9300-48T</t>
+  </si>
+  <si>
+    <t>switching.csv row 176</t>
+  </si>
+  <si>
+    <t>C9300: 48x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48P</t>
+  </si>
+  <si>
+    <t>switching.csv row 177</t>
+  </si>
+  <si>
+    <t>C9300: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48U</t>
+  </si>
+  <si>
+    <t>switching.csv row 178</t>
+  </si>
+  <si>
+    <t>C9300: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48UB</t>
+  </si>
+  <si>
+    <t>switching.csv row 179</t>
+  </si>
+  <si>
+    <t>C9300-48H</t>
+  </si>
+  <si>
+    <t>switching.csv row 180</t>
+  </si>
+  <si>
+    <t>C9300: 48x UPOE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48UXM</t>
+  </si>
+  <si>
+    <t>switching.csv row 181</t>
+  </si>
+  <si>
+    <t>C9300: 48x UPOE 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48UN</t>
+  </si>
+  <si>
+    <t>switching.csv row 182</t>
+  </si>
+  <si>
+    <t>C9300: 48x UPOE 5G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-24S</t>
+  </si>
+  <si>
+    <t>switching.csv row 183</t>
+  </si>
+  <si>
+    <t>C9300: 24x 1G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300-48S</t>
+  </si>
+  <si>
+    <t>switching.csv row 184</t>
+  </si>
+  <si>
+    <t>C9300: 48x 1G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24T-4G</t>
+  </si>
+  <si>
+    <t>C9300L</t>
+  </si>
+  <si>
+    <t>switching.csv row 190</t>
+  </si>
+  <si>
+    <t>C9300L: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 191</t>
+  </si>
+  <si>
+    <t>C9300L: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 192</t>
+  </si>
+  <si>
+    <t>C9300L: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 193</t>
+  </si>
+  <si>
+    <t>C9300L: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48PF-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 194</t>
+  </si>
+  <si>
+    <t>C9300L-24T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 195</t>
+  </si>
+  <si>
+    <t>C9300L: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 196</t>
+  </si>
+  <si>
+    <t>C9300L: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24UXG-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 197</t>
+  </si>
+  <si>
+    <t>C9300L: 24x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 198</t>
+  </si>
+  <si>
+    <t>C9300L: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 199</t>
+  </si>
+  <si>
+    <t>C9300L: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48PF-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 200</t>
+  </si>
+  <si>
+    <t>C9300L-48UXG-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 201</t>
+  </si>
+  <si>
+    <t>C9300L: 48x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-24UXG-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 202</t>
+  </si>
+  <si>
+    <t>C9300L: 24x UPOE 10G Copper downlinks and 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300L-48UXG-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 203</t>
+  </si>
+  <si>
+    <t>C9300L: 48x UPOE 10G Copper downlinks and 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300LM-48UX-4Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 204</t>
+  </si>
+  <si>
+    <t>C9300L: 48x UPOE 10G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300LM-48T-4Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 205</t>
+  </si>
+  <si>
+    <t>C9300L: 48x 1G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300LM-24U-4Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 206</t>
+  </si>
+  <si>
+    <t>C9300L: 24x UPOE 1G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48HX</t>
+  </si>
+  <si>
+    <t>C9300X</t>
+  </si>
+  <si>
+    <t>switching.csv row 213</t>
+  </si>
+  <si>
+    <t>C9300X: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48TX</t>
+  </si>
+  <si>
+    <t>switching.csv row 214</t>
+  </si>
+  <si>
+    <t>C9300X: 48x 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-48HXN</t>
+  </si>
+  <si>
+    <t>switching.csv row 215</t>
+  </si>
+  <si>
+    <t>C9300X: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-24HX</t>
+  </si>
+  <si>
+    <t>switching.csv row 216</t>
+  </si>
+  <si>
+    <t>C9300X: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-12Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 217</t>
+  </si>
+  <si>
+    <t>C9300X: 12x 25G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-24Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 218</t>
+  </si>
+  <si>
+    <t>C9300X: 24x 25G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9404R</t>
+  </si>
+  <si>
+    <t>C9400</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9400-series-switches/nb-06-cat9400-ser-data-sheet-cte-en.html</t>
+  </si>
+  <si>
+    <t>access, distribution</t>
+  </si>
+  <si>
+    <t>10, 40</t>
+  </si>
+  <si>
+    <t>switching.csv row 219</t>
+  </si>
+  <si>
+    <t>C9400: 96x Dependent on Line Card Modular downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>Stackwise Virtual stacking supported for 2 switches (DNA Advantage)</t>
+  </si>
+  <si>
+    <t>C9407R</t>
+  </si>
+  <si>
+    <t>switching.csv row 220</t>
+  </si>
+  <si>
+    <t>C9400: 240x Dependent on Line Card Modular downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9410R</t>
+  </si>
+  <si>
+    <t>switching.csv row 221</t>
+  </si>
+  <si>
+    <t>C9400: 384x Dependent on Line Card Modular downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9500X-28C8D</t>
+  </si>
+  <si>
+    <t>C9500</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-9500-series-switches/series.html</t>
+  </si>
+  <si>
+    <t>core, distribution</t>
+  </si>
+  <si>
+    <t>40, 100</t>
+  </si>
+  <si>
+    <t>40, 100, 200, 400</t>
+  </si>
+  <si>
+    <t>switching.csv row 238</t>
+  </si>
+  <si>
+    <t>C9500: 36x 100G / 400G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>DNA Advantage is required for Stackwise Virtual stacking!</t>
+  </si>
+  <si>
+    <t>C9500X-60L4D</t>
+  </si>
+  <si>
+    <t>10, 25, 50</t>
+  </si>
+  <si>
+    <t>switching.csv row 239</t>
+  </si>
+  <si>
+    <t>C9500: 64x 50G / 400G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9500-32C</t>
+  </si>
+  <si>
+    <t>switching.csv row 240</t>
+  </si>
+  <si>
+    <t>C9500: 32x 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>switching.csv row 241</t>
+  </si>
+  <si>
+    <t>C9500: 32x 40G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>DNA Advantage is required for Stackwise Virtual stacking! Ports can also be used as 16x 100G</t>
+  </si>
+  <si>
+    <t>C9500-48Y4C</t>
+  </si>
+  <si>
+    <t>switching.csv row 242</t>
+  </si>
+  <si>
+    <t>C9500: 48x 25G Fiber downlinks and 4x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9500-24Y4C</t>
+  </si>
+  <si>
+    <t>switching.csv row 243</t>
+  </si>
+  <si>
+    <t>C9500: 24x 25G Fiber downlinks and 4x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9500-16X</t>
+  </si>
+  <si>
+    <t>NMs: none</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9500-series-switches/c9500-16x-switch-nm-c9500-nm-8x-nm-2q-eol.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 244</t>
+  </si>
+  <si>
+    <t>C9500: 16x 10G Fiber downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9500-16X-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 245</t>
+  </si>
+  <si>
+    <t>C9500: 16x 10G Fiber downlinks and 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9606R</t>
+  </si>
+  <si>
+    <t>C9600</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/td/docs/switches/lan/catalyst9600/software/release/17-12/release_notes/ol-17-12-9600/introduction.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 248</t>
+  </si>
+  <si>
+    <t>C9600: 192x Dependent on Line Card Modular downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-24T</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9000-switches/c9000-smart-switches-faq.html</t>
+  </si>
+  <si>
+    <t>25, 100</t>
+  </si>
+  <si>
+    <t>switching.csv row 256</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 24x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>AI ready hardware using Cisco Silicon One ASICs</t>
+  </si>
+  <si>
+    <t>C9350-48T</t>
+  </si>
+  <si>
+    <t>switching.csv row 257</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-24P</t>
+  </si>
+  <si>
+    <t>switching.csv row 258</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-48P</t>
+  </si>
+  <si>
+    <t>switching.csv row 259</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-24U</t>
+  </si>
+  <si>
+    <t>switching.csv row 260</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-48U</t>
+  </si>
+  <si>
+    <t>switching.csv row 261</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-48TX</t>
+  </si>
+  <si>
+    <t>switching.csv row 262</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-24HX</t>
+  </si>
+  <si>
+    <t>switching.csv row 263</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-48HX</t>
+  </si>
+  <si>
+    <t>switching.csv row 264</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9350-48HXN</t>
+  </si>
+  <si>
+    <t>switching.csv row 265</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>C9550-24L4CD</t>
+  </si>
+  <si>
+    <t>C9550 SmartSwitch</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/networking/switches/c9550-series-smart-switches-ds.html</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>switching.csv row 269</t>
+  </si>
+  <si>
+    <t>C9550 SmartSwitch: 24 ports 50/25/10/1G downlinks, four 100/40G or two 400G ports as fixed uplinks</t>
+  </si>
+  <si>
+    <t>C9550-48L4CD</t>
+  </si>
+  <si>
+    <t>switching.csv row 270</t>
+  </si>
+  <si>
+    <t>C9550 SmartSwitch: 48 ports 50/25/10/1G downlinks, four 100/40G or two 400G ports as fixed uplinks</t>
+  </si>
+  <si>
+    <t>C9550-96L4D</t>
+  </si>
+  <si>
+    <t>switching.csv row 271</t>
+  </si>
+  <si>
+    <t>C9550 SmartSwitch: 96 ports 50/25/10/1G downlinks, four 400/100/40G ports as fixed uplinks</t>
+  </si>
+  <si>
+    <t>C9610R</t>
+  </si>
+  <si>
+    <t>C9610 SmartSwitch</t>
+  </si>
+  <si>
+    <t>switching.csv row 272</t>
+  </si>
+  <si>
+    <t>C9610 SmartSwitch: 384x Dependent on Line Card Modular downlinks and Modular uplinks</t>
+  </si>
+  <si>
+    <t>IE-1000-4T1T-LM</t>
+  </si>
+  <si>
+    <t>IE1000</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/industrial-ethernet-1000-series-switches/datasheet-c78-737277.html</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>rugged, redundant_psu, dc_power</t>
+  </si>
+  <si>
+    <t>switching.csv row 279</t>
+  </si>
+  <si>
+    <t>IE1000 with 4 FE Copper ports and 1 FE Copper uplinks, Rugged</t>
+  </si>
+  <si>
+    <t>rugged, Redundant PSU, DC Power</t>
+  </si>
+  <si>
+    <t>IE-1000-6T2T-LM</t>
+  </si>
+  <si>
+    <t>switching.csv row 280</t>
+  </si>
+  <si>
+    <t>IE1000 with 6 FE Copper ports and 2 FE Copper uplinks, Rugged</t>
+  </si>
+  <si>
+    <t>IE-1000-4P2S-LM</t>
+  </si>
+  <si>
+    <t>rugged, poe, redundant_psu, dc_power</t>
+  </si>
+  <si>
+    <t>switching.csv row 281</t>
+  </si>
+  <si>
+    <t>IE1000 with 4 FE Copper PoE+ ports and 2 GE SFP uplinks, Rugged</t>
+  </si>
+  <si>
+    <t>rugged, PoE, Redundant PSU, DC Power</t>
+  </si>
+  <si>
+    <t>IE-1000-8P2S-LM</t>
+  </si>
+  <si>
+    <t>switching.csv row 282</t>
+  </si>
+  <si>
+    <t>IE1000 with 8 FE Copper PoE+ ports and 2 GE SFP uplinks, Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-4T2S</t>
+  </si>
+  <si>
+    <t>IE3100</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/networking/industrial-switches/catalyst-ie3100-rugged-series/catalyst-ie3100-rugged-series-ds.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 283</t>
+  </si>
+  <si>
+    <t>IE3100: 4x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-8T2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 284</t>
+  </si>
+  <si>
+    <t>IE3100: 8x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-8T4S</t>
+  </si>
+  <si>
+    <t>switching.csv row 285</t>
+  </si>
+  <si>
+    <t>IE3100: 8x 1G Copper downlinks and 4x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-18T2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 286</t>
+  </si>
+  <si>
+    <t>IE3100: 18x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-18T2C-CC</t>
+  </si>
+  <si>
+    <t>switching.csv row 287</t>
+  </si>
+  <si>
+    <t>IE3100: 18x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged, Conformal Coating</t>
+  </si>
+  <si>
+    <t>IE-3105-8T2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 288</t>
+  </si>
+  <si>
+    <t>IE-3105-18T2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 289</t>
+  </si>
+  <si>
+    <t>IE-3100-4P2S</t>
+  </si>
+  <si>
+    <t>switching.csv row 290</t>
+  </si>
+  <si>
+    <t>IE3100: 4x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-3P1U2S</t>
+  </si>
+  <si>
+    <t>switching.csv row 291</t>
+  </si>
+  <si>
+    <t>IE3100: 4x 4PPoE 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-8P2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 292</t>
+  </si>
+  <si>
+    <t>IE3100: 8x PoE+ 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100-6P2U2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 293</t>
+  </si>
+  <si>
+    <t>IE3100: 8x 4PPoE 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3100H-6FT2T-E</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/networking/industrial-switches/catalyst-ie3100-heavy-duty-series/catalyst-ie3100-heavy-duty-series-ds.html#Orderinginformation</t>
+  </si>
+  <si>
+    <t>rugged, dc_power, heavyduty</t>
+  </si>
+  <si>
+    <t>switching.csv row 294</t>
+  </si>
+  <si>
+    <t>IE3100: IP67 w/6FE 2GE M12 Ports, Rugged Heavy Duty</t>
+  </si>
+  <si>
+    <t>rugged, DC power, Heavyduty</t>
+  </si>
+  <si>
+    <t>IE-3100H-8T-E</t>
+  </si>
+  <si>
+    <t>switching.csv row 295</t>
+  </si>
+  <si>
+    <t>IE3100: IP67 w/8GE M12 Ports, Rugged Heavy Duty</t>
+  </si>
+  <si>
+    <t>IE-3200-8T2S</t>
+  </si>
+  <si>
+    <t>IE3200</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3200-rugged-series/cat-ie3200-rugged-series-ds.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 296</t>
+  </si>
+  <si>
+    <t>IE-3200: 8x 1G Copper downlinks and 2x 1G SFP Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3200-8P2S</t>
+  </si>
+  <si>
+    <t>switching.csv row 297</t>
+  </si>
+  <si>
+    <t>IE-3200: 8x PoE+ 1G Copper downlinks and 2x 1G SFP Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3300-8P2S</t>
+  </si>
+  <si>
+    <t>IE3300</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3300-rugged-series/catalyst-ie3300-rugged-series-ds.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 298</t>
+  </si>
+  <si>
+    <t>IE3300: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>rugged, PoE, Redundant PSU, DC power</t>
+  </si>
+  <si>
+    <t>IE-3300-8U2X</t>
+  </si>
+  <si>
+    <t>switching.csv row 299</t>
+  </si>
+  <si>
+    <t>IE3300: 8x 4PPoE 1G Copper downlinks and 2x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3300-8T2S</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-ie3300-rugged-series/series.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 300</t>
+  </si>
+  <si>
+    <t>IE3300: 8x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3300-8T2X</t>
+  </si>
+  <si>
+    <t>switching.csv row 301</t>
+  </si>
+  <si>
+    <t>IE3300: 8x 1G Copper downlinks and 2x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3400-8T2S</t>
+  </si>
+  <si>
+    <t>IE3400</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3400-rugged-series/cat-ie3400-rugged-series-ds.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 310</t>
+  </si>
+  <si>
+    <t>IE3400: 8x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>rugged, Redundant PSU, DC power</t>
+  </si>
+  <si>
+    <t>IE-3400-8P2S</t>
+  </si>
+  <si>
+    <t>switching.csv row 311</t>
+  </si>
+  <si>
+    <t>IE3400: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-3400H-8FT</t>
+  </si>
+  <si>
+    <t>switching.csv row 312</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 8 FE M12 interfaces, IP67</t>
+  </si>
+  <si>
+    <t>Heavy Duty industrial switch with M12 connectors</t>
+  </si>
+  <si>
+    <t>IE-3400H-16FT</t>
+  </si>
+  <si>
+    <t>switching.csv row 313</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 16 FE M12 interfaces, IP67</t>
+  </si>
+  <si>
+    <t>IE-3400H-24FT</t>
+  </si>
+  <si>
+    <t>switching.csv row 314</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 24 FE M12 interfaces, IP67</t>
+  </si>
+  <si>
+    <t>IE-3400H-8T</t>
+  </si>
+  <si>
+    <t>switching.csv row 315</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 8 GE M12 interfaces, IP67,</t>
+  </si>
+  <si>
+    <t>IE-3400H-16T</t>
+  </si>
+  <si>
+    <t>switching.csv row 316</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 16 GE M12 interfaces, IP67</t>
+  </si>
+  <si>
+    <t>IE-3400H-24T</t>
+  </si>
+  <si>
+    <t>switching.csv row 317</t>
+  </si>
+  <si>
+    <t>Catalyst IE3400 Heavy Duty w/ 24 GE M12 interfaces, IP67</t>
+  </si>
+  <si>
+    <t>IE-9310-26S2C</t>
+  </si>
+  <si>
+    <t>IE9300</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-ie9300-rugged-series/series.html</t>
+  </si>
+  <si>
+    <t>switching.csv row 328</t>
+  </si>
+  <si>
+    <t>IE9300: 26x 1G Fiber downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-9320-26S2C</t>
+  </si>
+  <si>
+    <t>rugged, stacking, redundant_psu, dc_power</t>
+  </si>
+  <si>
+    <t>switching.csv row 329</t>
+  </si>
+  <si>
+    <t>rugged, Stacking, Redundant PSU, DC Power</t>
+  </si>
+  <si>
+    <t>IE-9320-22S2C4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 330</t>
+  </si>
+  <si>
+    <t>IE9300: 24x 1G Fiber downlinks and 4x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-9320-24P4S</t>
+  </si>
+  <si>
+    <t>rugged, poe, stacking, redundant_psu, dc_power</t>
+  </si>
+  <si>
+    <t>switching.csv row 331</t>
+  </si>
+  <si>
+    <t>IE9300: 24x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>rugged, PoE, Stacking, Redundant PSU, DC Power</t>
+  </si>
+  <si>
+    <t>IE-9320-24T4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 332</t>
+  </si>
+  <si>
+    <t>IE9300: 24x 1G Copper downlinks and 4x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-9320-24P4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 333</t>
+  </si>
+  <si>
+    <t>IE9300: 24x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>IE-9320-16P8U4X</t>
+  </si>
+  <si>
+    <t>1, 2.5</t>
+  </si>
+  <si>
+    <t>rugged, poe, stacking, multigigabit, redundant_psu, dc_power</t>
+  </si>
+  <si>
+    <t>switching.csv row 334</t>
+  </si>
+  <si>
+    <t>IE9300: 16 ports 1G Copper PoE+ and 8 ports 2.5G 4PPoE downlinks and 4x 1/10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>rugged, PoE, Stacking, Multigigabit, Redundant PSU, DC Power</t>
+  </si>
+  <si>
+    <t>IE-9310-16P8S4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 335</t>
+  </si>
+  <si>
+    <t>IE9300: 16x PoE+ 1G Copper and 8x 1G Fiber downlinks and 4x 10G Fiber uplinks Rugged</t>
+  </si>
+  <si>
+    <t>CBS220-8T-E-2G</t>
+  </si>
+  <si>
+    <t>CBS220</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/small-business-220-series-smart-plus-switches/220-series-smart-switches-eol.html</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/switches/cisco-business-switches/index.html</t>
+  </si>
+  <si>
+    <t>smart_managed, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 336</t>
+  </si>
+  <si>
+    <t>CBS220: 8x 1G Copper downlinks and 2x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>smart managed, SMB</t>
+  </si>
+  <si>
+    <t>CBS220-8P-E-2G</t>
+  </si>
+  <si>
+    <t>smart_managed, poe, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 337</t>
+  </si>
+  <si>
+    <t>CBS220: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>smart managed, PoE, SMB</t>
+  </si>
+  <si>
+    <t>CBS220-8FP-E-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 338</t>
+  </si>
+  <si>
+    <t>CBS220: 8x PoE+ (Full) 1G Copper downlinks and 2x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-16T-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 339</t>
+  </si>
+  <si>
+    <t>CBS220: 16x 1G Copper downlinks and 2x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-16P-2G</t>
+  </si>
+  <si>
+    <t>switching.csv row 340</t>
+  </si>
+  <si>
+    <t>CBS220: 16x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 341</t>
+  </si>
+  <si>
+    <t>CBS220: 24x 1G Copper downlinks and 4x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 342</t>
+  </si>
+  <si>
+    <t>CBS220: 24x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24FP-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 343</t>
+  </si>
+  <si>
+    <t>CBS220: 24x PoE+ (Full) 1G Copper downlinks and 4x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-48T-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 344</t>
+  </si>
+  <si>
+    <t>CBS220: 48x 1G Copper downlinks and 4x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-48P-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 345</t>
+  </si>
+  <si>
+    <t>CBS220: 48x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 346</t>
+  </si>
+  <si>
+    <t>CBS220: 24x 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 347</t>
+  </si>
+  <si>
+    <t>CBS220: 24x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-24FP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 348</t>
+  </si>
+  <si>
+    <t>CBS220: 24x PoE+ (Full) 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-48T-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 349</t>
+  </si>
+  <si>
+    <t>CBS220: 48x 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-48P-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 350</t>
+  </si>
+  <si>
+    <t>CBS220: 48x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS220-48FP-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 351</t>
+  </si>
+  <si>
+    <t>CBS220: 48x PoE+ (Full) 1G Copper downlinks and 4x 10G Fiber uplinks</t>
+  </si>
+  <si>
+    <t>CBS110-5T-D</t>
+  </si>
+  <si>
+    <t>CBS110</t>
+  </si>
+  <si>
+    <t>unmanaged, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 352</t>
+  </si>
+  <si>
+    <t>CBS110: 5x 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>Unmanaged</t>
+  </si>
+  <si>
+    <t>unmanaged, SMB</t>
+  </si>
+  <si>
+    <t>CBS110-8T-D</t>
+  </si>
+  <si>
+    <t>switching.csv row 353</t>
+  </si>
+  <si>
+    <t>CBS110: 8x 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>CBS110-8PP-D</t>
+  </si>
+  <si>
+    <t>unmanaged, poe, smb</t>
+  </si>
+  <si>
+    <t>switching.csv row 354</t>
+  </si>
+  <si>
+    <t>CBS110: 8x PoE (Partial) 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>unmanaged, PoE, SMB</t>
+  </si>
+  <si>
+    <t>CBS110-16T</t>
+  </si>
+  <si>
+    <t>switching.csv row 355</t>
+  </si>
+  <si>
+    <t>CBS110: 16x 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>CBS110-16PP</t>
+  </si>
+  <si>
+    <t>switching.csv row 356</t>
+  </si>
+  <si>
+    <t>CBS110: 16x PoE (Partial) 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>CBS110-24T</t>
+  </si>
+  <si>
+    <t>switching.csv row 357</t>
+  </si>
+  <si>
+    <t>CBS110: 24x 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>CBS110-24PP</t>
+  </si>
+  <si>
+    <t>switching.csv row 358</t>
+  </si>
+  <si>
+    <t>CBS110: 24x PoE (Partial) 1G Copper downlinks Unmanaged</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>speed_gbps</t>
+  </si>
+  <si>
+    <t>C9300-NM-4G</t>
   </si>
   <si>
     <t>switching.csv row 57</t>
   </si>
   <si>
-    <t>9200L-M:24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Multigigabit, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9200L-24PXG-2Y-M</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>9300-M: 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-8X</t>
+  </si>
+  <si>
+    <t>switching.csv row 58</t>
+  </si>
+  <si>
+    <t>9300-M: 8x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-2Q</t>
   </si>
   <si>
     <t>switching.csv row 59</t>
   </si>
   <si>
-    <t>9200L-M: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PXG-4X-M</t>
+    <t>9300-M: 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-2Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 60</t>
+  </si>
+  <si>
+    <t>9300-M: 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-4M</t>
   </si>
   <si>
     <t>switching.csv row 61</t>
   </si>
   <si>
-    <t>9200L-M: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PXG-2Y-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 63</t>
-  </si>
-  <si>
-    <t>9200L-M: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24T-M</t>
-  </si>
-  <si>
-    <t>9300-M</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9300-series-switches/datasheet-listing.html</t>
-  </si>
-  <si>
-    <t>1, 10, 25, 40</t>
-  </si>
-  <si>
-    <t>stacking, stackpower, redundant_psu, fan</t>
-  </si>
-  <si>
-    <t>switching.csv row 65</t>
-  </si>
-  <si>
-    <t>9300-M: 24x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>Meraki Switches: Add powercord separately (ma-pwr-cord-eu)!</t>
-  </si>
-  <si>
-    <t>Stacking, StackPower, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9300-24P-M</t>
-  </si>
-  <si>
-    <t>poe, stacking, stackpower, redundant_psu, fan</t>
-  </si>
-  <si>
-    <t>switching.csv row 66</t>
-  </si>
-  <si>
-    <t>9300-M: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, StackPower, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9300-24U-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 67</t>
-  </si>
-  <si>
-    <t>9300-M: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48T-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 68</t>
-  </si>
-  <si>
-    <t>9300-M: 48x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48P-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 69</t>
-  </si>
-  <si>
-    <t>9300-M: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48U-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 70</t>
-  </si>
-  <si>
-    <t>9300-M: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24UX-M</t>
-  </si>
-  <si>
-    <t>poe, stacking, multigigabit, stackpower, redundant_psu, fan</t>
-  </si>
-  <si>
-    <t>switching.csv row 71</t>
-  </si>
-  <si>
-    <t>9300-M: 24x UPOE 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Multigigabit, StackPower, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9300-48UXM-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 72</t>
-  </si>
-  <si>
-    <t>9300-M: 48x UPOE 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48UN-M</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>switching.csv row 73</t>
-  </si>
-  <si>
-    <t>9300-M: 48x UPOE 5G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24S-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 74</t>
-  </si>
-  <si>
-    <t>9300-M: 24x 1G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48S-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 75</t>
-  </si>
-  <si>
-    <t>9300-M: 48x 1G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24T-4X-M</t>
-  </si>
-  <si>
-    <t>9300L-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 82</t>
-  </si>
-  <si>
-    <t>9300L-M: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48T-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 83</t>
-  </si>
-  <si>
-    <t>9300L-M: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24P-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 84</t>
-  </si>
-  <si>
-    <t>9300L-M: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48P-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 85</t>
-  </si>
-  <si>
-    <t>9300L-M: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48PF-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 86</t>
-  </si>
-  <si>
-    <t>C9300L-24UXG-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 87</t>
-  </si>
-  <si>
-    <t>9300L-M: 24x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48UXG-4X-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 88</t>
-  </si>
-  <si>
-    <t>9300L-M: 48x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48TX-M</t>
-  </si>
-  <si>
-    <t>9300X-M</t>
-  </si>
-  <si>
-    <t>10, 25, 100</t>
-  </si>
-  <si>
-    <t>stacking, multigigabit, stackpower, redundant_psu, fan</t>
-  </si>
-  <si>
-    <t>switching.csv row 89</t>
-  </si>
-  <si>
-    <t>9300X-M: 48x 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>Stacking, Multigigabit, StackPower, Redundant PSU, Fan</t>
-  </si>
-  <si>
-    <t>C9300X-24HX-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 90</t>
-  </si>
-  <si>
-    <t>9300X-M: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48HX-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 91</t>
-  </si>
-  <si>
-    <t>9300X-M: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48HXN-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 92</t>
-  </si>
-  <si>
-    <t>9300X-M: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-12Y-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 93</t>
-  </si>
-  <si>
-    <t>9300X-M: 12x 25G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-24Y-M</t>
-  </si>
-  <si>
-    <t>switching.csv row 94</t>
-  </si>
-  <si>
-    <t>9300X-M: 24x 25G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C1200-8T-D</t>
-  </si>
-  <si>
-    <t>C1200</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/switches/catalyst-1200-series-switches/datasheet-listing.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 100</t>
-  </si>
-  <si>
-    <t>C1200: 8x 1G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C1200 series don't support stacking!</t>
-  </si>
-  <si>
-    <t>C1200-8T-E-2G</t>
-  </si>
-  <si>
-    <t>copper, fiber</t>
-  </si>
-  <si>
-    <t>switching.csv row 101</t>
-  </si>
-  <si>
-    <t>C1200: 8x 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-8P-E-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 102</t>
-  </si>
-  <si>
-    <t>C1200: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-8FP-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 103</t>
-  </si>
-  <si>
-    <t>C1200: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-16T-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 104</t>
-  </si>
-  <si>
-    <t>C1200: 16x 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-16P-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 105</t>
-  </si>
-  <si>
-    <t>C1200: 16x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 106</t>
-  </si>
-  <si>
-    <t>C1200: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 107</t>
-  </si>
-  <si>
-    <t>C1200: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24FP-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 108</t>
-  </si>
-  <si>
-    <t>C1200-48T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 109</t>
-  </si>
-  <si>
-    <t>C1200: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-48P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 110</t>
-  </si>
-  <si>
-    <t>C1200: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 111</t>
-  </si>
-  <si>
-    <t>C1200: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 112</t>
-  </si>
-  <si>
-    <t>C1200: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-24FP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 113</t>
-  </si>
-  <si>
-    <t>C1200-48T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 114</t>
-  </si>
-  <si>
-    <t>C1200: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1200-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 115</t>
-  </si>
-  <si>
-    <t>C1200: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-8T-E-2G</t>
-  </si>
-  <si>
-    <t>C1300</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-1200-series-switches/nb-06-cat1200-1300-ser-aag-cte-en.pdf</t>
-  </si>
-  <si>
-    <t>switching.csv row 116</t>
-  </si>
-  <si>
-    <t>C1300: 8x 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300 series with 1G uplinks can't stack</t>
-  </si>
-  <si>
-    <t>C1300-8P-E-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 117</t>
-  </si>
-  <si>
-    <t>C1300: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-8FP-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 118</t>
-  </si>
-  <si>
-    <t>C1300: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-16T-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 119</t>
-  </si>
-  <si>
-    <t>C1300: 16x 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-16P-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 120</t>
-  </si>
-  <si>
-    <t>C1300: 16x PoE+ 1G Copper downlinks and 2x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-16FP-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 121</t>
-  </si>
-  <si>
-    <t>C1300-24T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 122</t>
-  </si>
-  <si>
-    <t>C1300: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-24P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 123</t>
-  </si>
-  <si>
-    <t>C1300: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-24FP-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 124</t>
-  </si>
-  <si>
-    <t>PoE,SMB</t>
-  </si>
-  <si>
-    <t>C1300-48T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 125</t>
-  </si>
-  <si>
-    <t>C1300: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-48P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 126</t>
-  </si>
-  <si>
-    <t>C1300: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-48FP-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 127</t>
-  </si>
-  <si>
-    <t>C1300-16P-4X</t>
-  </si>
-  <si>
-    <t>poe, stacking, fan, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 128</t>
-  </si>
-  <si>
-    <t>C1300: 16x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Fan, SMB</t>
-  </si>
-  <si>
-    <t>C1300-24T-4X</t>
-  </si>
-  <si>
-    <t>stacking, fan, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 129</t>
-  </si>
-  <si>
-    <t>C1300: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>Stacking, Fan, SMB</t>
-  </si>
-  <si>
-    <t>C1300-24P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 130</t>
-  </si>
-  <si>
-    <t>C1300: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-24FP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 131</t>
-  </si>
-  <si>
-    <t>C1300-48T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 132</t>
-  </si>
-  <si>
-    <t>C1300: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 133</t>
-  </si>
-  <si>
-    <t>C1300: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-48FP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 134</t>
-  </si>
-  <si>
-    <t>C1300-8MGP-2X</t>
-  </si>
-  <si>
-    <t>poe, stacking, multigigabit, fan, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 135</t>
-  </si>
-  <si>
-    <t>C1300: 8x PoE+ 2.5G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Stacking, Multigigabit, Fan, SMB</t>
-  </si>
-  <si>
-    <t>C1300-24MGP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 136</t>
-  </si>
-  <si>
-    <t>C1300: 24x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-48MGP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 137</t>
-  </si>
-  <si>
-    <t>C1300: 48x PoE+ 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-12XT-2X</t>
-  </si>
-  <si>
-    <t>switching.csv row 138</t>
-  </si>
-  <si>
-    <t>C1300: 12x 10G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300-12XS</t>
-  </si>
-  <si>
-    <t>switching.csv row 139</t>
-  </si>
-  <si>
-    <t>C1300: 12x 10G Copper/ Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C1300-16XTS</t>
-  </si>
-  <si>
-    <t>switching.csv row 140</t>
-  </si>
-  <si>
-    <t>C1300: 16x 10G Copper/ Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C1300-24XS</t>
-  </si>
-  <si>
-    <t>switching.csv row 141</t>
-  </si>
-  <si>
-    <t>C1300: 24x 10G Copper/ Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C1300-24XT</t>
+    <t>9300-M: 4x 10Gbps Multigigabit Copper uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-BLANK</t>
+  </si>
+  <si>
+    <t>switching.csv row 62</t>
+  </si>
+  <si>
+    <t>C9300X-NM-8M</t>
+  </si>
+  <si>
+    <t>switching.csv row 76</t>
+  </si>
+  <si>
+    <t>9300X-M: 8x 10Gbps Multigigabit Copper uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-NM-8Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 77</t>
+  </si>
+  <si>
+    <t>9300X-M: 8x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-NM-2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 78</t>
+  </si>
+  <si>
+    <t>9300X-M: 2x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-NM-4C</t>
+  </si>
+  <si>
+    <t>switching.csv row 79</t>
+  </si>
+  <si>
+    <t>9300X-M: 4x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300X-NM-BLANK</t>
+  </si>
+  <si>
+    <t>switching.csv row 80</t>
+  </si>
+  <si>
+    <t>C9200-NM-2Y</t>
   </si>
   <si>
     <t>switching.csv row 142</t>
   </si>
   <si>
-    <t>C1300: 24x 10G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C1300-24XTS</t>
+    <t>C9200: 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-2Q</t>
   </si>
   <si>
     <t>switching.csv row 143</t>
   </si>
   <si>
-    <t>C1300: 24x 10G Hybrid downlinks</t>
-  </si>
-  <si>
-    <t>C1300X-24T-4X</t>
-  </si>
-  <si>
-    <t>C1300X</t>
+    <t>C9200: 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-4G</t>
   </si>
   <si>
     <t>switching.csv row 144</t>
   </si>
   <si>
-    <t>C1300X: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-48T-4X</t>
+    <t>C9200: 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-4X</t>
   </si>
   <si>
     <t>switching.csv row 145</t>
   </si>
   <si>
-    <t>C1300X: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-24P-4X</t>
+    <t>C9200: 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-BLANK</t>
   </si>
   <si>
     <t>switching.csv row 146</t>
   </si>
   <si>
-    <t>C1300X: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 147</t>
-  </si>
-  <si>
-    <t>C1300X: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-24MU-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 148</t>
-  </si>
-  <si>
-    <t>C1300X: 24x UPOE 2.5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-10NU-2X</t>
-  </si>
-  <si>
-    <t>switching.csv row 149</t>
-  </si>
-  <si>
-    <t>C1300X: 10x UPOE 5G Copper downlinks and 2x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-24NGU-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 150</t>
-  </si>
-  <si>
-    <t>C1300X: 24x UPOE 5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C1300X-48NGU-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 151</t>
-  </si>
-  <si>
-    <t>C1300X: 48x UPOE 5G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-24T</t>
-  </si>
-  <si>
-    <t>C9200</t>
-  </si>
-  <si>
-    <t>switching.csv row 152</t>
-  </si>
-  <si>
-    <t>C9200: 24x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>No support for BGP, PTP, MACSEC-256 on 9200/9200L series</t>
-  </si>
-  <si>
-    <t>C9200-24P</t>
-  </si>
-  <si>
-    <t>switching.csv row 153</t>
-  </si>
-  <si>
-    <t>C9200: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9200-24PB</t>
-  </si>
-  <si>
-    <t>switching.csv row 154</t>
-  </si>
-  <si>
-    <t>C9200-24PXG</t>
-  </si>
-  <si>
-    <t>switching.csv row 155</t>
-  </si>
-  <si>
-    <t>C9200: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9200-48T</t>
-  </si>
-  <si>
-    <t>switching.csv row 156</t>
-  </si>
-  <si>
-    <t>C9200: 48x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9200-48P</t>
-  </si>
-  <si>
-    <t>switching.csv row 157</t>
-  </si>
-  <si>
-    <t>C9200: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9200-48PL</t>
-  </si>
-  <si>
-    <t>switching.csv row 158</t>
-  </si>
-  <si>
-    <t>C9200-48PB</t>
-  </si>
-  <si>
-    <t>switching.csv row 159</t>
-  </si>
-  <si>
-    <t>C9200-48PXG</t>
-  </si>
-  <si>
-    <t>switching.csv row 160</t>
-  </si>
-  <si>
-    <t>C9200: 48 ports full PoE+ (8 mGig ports up to 10G, 40 ports up to 1G) and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24T-4G</t>
-  </si>
-  <si>
-    <t>C9200L</t>
-  </si>
-  <si>
-    <t>on_prem, cloud</t>
-  </si>
-  <si>
-    <t>switching.csv row 166</t>
-  </si>
-  <si>
-    <t>C9200L: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 167</t>
-  </si>
-  <si>
-    <t>C9200L: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 168</t>
-  </si>
-  <si>
-    <t>C9200L: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 169</t>
-  </si>
-  <si>
-    <t>C9200L: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PL-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 170</t>
-  </si>
-  <si>
-    <t>C9200L-24T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 171</t>
-  </si>
-  <si>
-    <t>C9200L: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 172</t>
-  </si>
-  <si>
-    <t>C9200L: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 173</t>
-  </si>
-  <si>
-    <t>C9200L: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 174</t>
-  </si>
-  <si>
-    <t>C9200L: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PL-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 175</t>
-  </si>
-  <si>
-    <t>C9200L-24PXG-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 176</t>
-  </si>
-  <si>
-    <t>C9200L: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PXG-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 177</t>
-  </si>
-  <si>
-    <t>C9200L: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-24PXG-2Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 178</t>
-  </si>
-  <si>
-    <t>C9200L: 24 ports full PoE+ (8 mGig ports up to 10G, 16 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200L-48PXG-2Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 179</t>
-  </si>
-  <si>
-    <t>C9200L: 48 ports full POE+ (12 mGig ports up to 10G, 36 ports up to 1G) and 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200CX-12T-2X2G</t>
-  </si>
-  <si>
-    <t>C9200CX</t>
-  </si>
-  <si>
-    <t>1, 10</t>
-  </si>
-  <si>
-    <t>switching.csv row 180</t>
-  </si>
-  <si>
-    <t>C9200CX: 12x 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>No support for stacking!</t>
-  </si>
-  <si>
-    <t>C9200CX-12P-2X2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 181</t>
-  </si>
-  <si>
-    <t>C9200CX: 12x PoE+ 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE</t>
-  </si>
-  <si>
-    <t>C9200CX-8P-2X2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 182</t>
-  </si>
-  <si>
-    <t>C9200CX: 8x PoE+ 1G Copper downlinks and 4x 1Gbps / 10Gbps Copper + Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200CX-8UXG-2X</t>
-  </si>
-  <si>
-    <t>poe, multigigabit</t>
-  </si>
-  <si>
-    <t>switching.csv row 183</t>
-  </si>
-  <si>
-    <t>C9200CX: 8 ports UPOE (4 mGig ports up to 10G, 4 ports up to 1G) and 2x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>PoE, Multigigabit</t>
-  </si>
-  <si>
-    <t>C9200CX-12P-2XGH</t>
-  </si>
-  <si>
-    <t>switching.csv row 184</t>
-  </si>
-  <si>
-    <t>C9200CX-8P-2XGH</t>
-  </si>
-  <si>
-    <t>switching.csv row 185</t>
-  </si>
-  <si>
-    <t>C9200CX-8UXG-2XH</t>
-  </si>
-  <si>
-    <t>switching.csv row 186</t>
-  </si>
-  <si>
-    <t>C9200CX:8 ports UPOE (4 mGig ports up to 10G, 4 ports up to 1G) and 2x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200CX-8PT-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 187</t>
-  </si>
-  <si>
-    <t>C9200CX: 8x PoE+ 1G Copper downlinks and 2x 1Gbps Copper uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24T</t>
-  </si>
-  <si>
-    <t>C9300</t>
-  </si>
-  <si>
-    <t>switching.csv row 188</t>
-  </si>
-  <si>
-    <t>C9300: 24x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24P</t>
+    <t>BLANK</t>
   </si>
   <si>
     <t>switching.csv row 189</t>
   </si>
   <si>
-    <t>C9300: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24U</t>
-  </si>
-  <si>
-    <t>switching.csv row 190</t>
-  </si>
-  <si>
-    <t>C9300: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24UB</t>
-  </si>
-  <si>
-    <t>switching.csv row 191</t>
-  </si>
-  <si>
-    <t>C9300-24H</t>
-  </si>
-  <si>
-    <t>switching.csv row 192</t>
-  </si>
-  <si>
-    <t>C9300: 24x UPOE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24UX</t>
-  </si>
-  <si>
-    <t>switching.csv row 193</t>
-  </si>
-  <si>
-    <t>C9300: 24x UPOE 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24UXB</t>
-  </si>
-  <si>
-    <t>switching.csv row 194</t>
-  </si>
-  <si>
-    <t>C9300-48T</t>
-  </si>
-  <si>
-    <t>switching.csv row 195</t>
-  </si>
-  <si>
-    <t>C9300: 48x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48P</t>
-  </si>
-  <si>
-    <t>switching.csv row 196</t>
-  </si>
-  <si>
-    <t>C9300: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48U</t>
-  </si>
-  <si>
-    <t>switching.csv row 197</t>
-  </si>
-  <si>
-    <t>C9300: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48UB</t>
-  </si>
-  <si>
-    <t>switching.csv row 198</t>
-  </si>
-  <si>
-    <t>C9300-48H</t>
-  </si>
-  <si>
-    <t>switching.csv row 199</t>
-  </si>
-  <si>
-    <t>C9300: 48x UPOE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48UXM</t>
-  </si>
-  <si>
-    <t>switching.csv row 200</t>
-  </si>
-  <si>
-    <t>C9300: 48x UPOE 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48UN</t>
-  </si>
-  <si>
-    <t>switching.csv row 201</t>
-  </si>
-  <si>
-    <t>C9300: 48x UPOE 5G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-24S</t>
-  </si>
-  <si>
-    <t>switching.csv row 202</t>
-  </si>
-  <si>
-    <t>C9300: 24x 1G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300-48S</t>
-  </si>
-  <si>
-    <t>switching.csv row 203</t>
-  </si>
-  <si>
-    <t>C9300: 48x 1G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24T-4G</t>
-  </si>
-  <si>
-    <t>C9300L</t>
-  </si>
-  <si>
-    <t>switching.csv row 209</t>
-  </si>
-  <si>
-    <t>C9300L: 24x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 210</t>
-  </si>
-  <si>
-    <t>C9300L: 24x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 211</t>
-  </si>
-  <si>
-    <t>C9300L: 48x 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 212</t>
-  </si>
-  <si>
-    <t>C9300L: 48x PoE+ 1G Copper downlinks and 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48PF-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 213</t>
-  </si>
-  <si>
-    <t>C9300L-24T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 214</t>
-  </si>
-  <si>
-    <t>C9300L: 24x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 215</t>
-  </si>
-  <si>
-    <t>C9300L: 24x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24UXG-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 216</t>
-  </si>
-  <si>
-    <t>C9300L: 24x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 217</t>
-  </si>
-  <si>
-    <t>C9300L: 48x 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 218</t>
-  </si>
-  <si>
-    <t>C9300L: 48x PoE+ 1G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48PF-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 219</t>
-  </si>
-  <si>
-    <t>C9300L-48UXG-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 220</t>
-  </si>
-  <si>
-    <t>C9300L: 48x UPOE 10G Copper downlinks and 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-24UXG-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 221</t>
-  </si>
-  <si>
-    <t>C9300L: 24x UPOE 10G Copper downlinks and 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300L-48UXG-2Q</t>
+    <t>C9400-SUP-1</t>
+  </si>
+  <si>
+    <t>fiber, hybrid</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2030-04-30</t>
+  </si>
+  <si>
+    <t>C9400X-SUP-2 / C9400X-SUP-2XL</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9400-series-switches/catalyst-9400-series-supervisor-module-eol.html</t>
   </si>
   <si>
     <t>switching.csv row 222</t>
   </si>
   <si>
-    <t>C9300L: 48x UPOE 10G Copper downlinks and 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300LM-48UX-4Y</t>
+    <t>C9400: 8x 10Gbps / 40Gbps Fiber / Hybrid uplinks</t>
+  </si>
+  <si>
+    <t>C9400-SUP-1XL</t>
   </si>
   <si>
     <t>switching.csv row 223</t>
   </si>
   <si>
-    <t>C9300L: 48x UPOE 10G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300LM-48T-4Y</t>
+    <t>C9400-LC-48U</t>
   </si>
   <si>
     <t>switching.csv row 224</t>
   </si>
   <si>
-    <t>C9300L: 48x 1G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300LM-24U-4Y</t>
+    <t>C9400: 48x UPOE 1G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48P</t>
   </si>
   <si>
     <t>switching.csv row 225</t>
   </si>
   <si>
-    <t>C9300L: 24x UPOE 1G Copper downlinks and 4x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48HX</t>
-  </si>
-  <si>
-    <t>C9300X</t>
+    <t>C9400: 48x PoE+ 1G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48T</t>
+  </si>
+  <si>
+    <t>switching.csv row 226</t>
+  </si>
+  <si>
+    <t>C9400: 48x 1G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48UX</t>
+  </si>
+  <si>
+    <t>switching.csv row 227</t>
+  </si>
+  <si>
+    <t>C9400: 48x UPOE 10G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-24XS</t>
+  </si>
+  <si>
+    <t>switching.csv row 228</t>
+  </si>
+  <si>
+    <t>C9400: 24x 10G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-24S</t>
+  </si>
+  <si>
+    <t>switching.csv row 229</t>
+  </si>
+  <si>
+    <t>C9400: 24x 1G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48S</t>
+  </si>
+  <si>
+    <t>switching.csv row 230</t>
+  </si>
+  <si>
+    <t>C9400: 48x 1G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48H</t>
+  </si>
+  <si>
+    <t>switching.csv row 231</t>
+  </si>
+  <si>
+    <t>C9400: 48x UPOE+ 1G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48HN</t>
   </si>
   <si>
     <t>switching.csv row 232</t>
   </si>
   <si>
-    <t>C9300X: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48TX</t>
+    <t>C9400: 48x UPOE+ 5G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48HX</t>
   </si>
   <si>
     <t>switching.csv row 233</t>
   </si>
   <si>
-    <t>C9300X: 48x 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-48HXN</t>
+    <t>C9400: 48x UPOE+ 10G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48TX</t>
   </si>
   <si>
     <t>switching.csv row 234</t>
   </si>
   <si>
-    <t>C9300X: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-24HX</t>
+    <t>C9400: 48x 10G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-48XS</t>
   </si>
   <si>
     <t>switching.csv row 235</t>
   </si>
   <si>
-    <t>C9300X: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-12Y</t>
+    <t>C9400: 48x 10G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-24XY</t>
   </si>
   <si>
     <t>switching.csv row 236</t>
   </si>
   <si>
-    <t>C9300X: 12x 25G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-24Y</t>
+    <t>C9400: 24x 25G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9400-LC-12QC</t>
   </si>
   <si>
     <t>switching.csv row 237</t>
   </si>
   <si>
-    <t>C9300X: 24x 25G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9404R</t>
-  </si>
-  <si>
-    <t>C9400</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9400-series-switches/nb-06-cat9400-ser-data-sheet-cte-en.html</t>
-  </si>
-  <si>
-    <t>access, distribution</t>
-  </si>
-  <si>
-    <t>10, 40</t>
-  </si>
-  <si>
-    <t>switching.csv row 238</t>
-  </si>
-  <si>
-    <t>C9400: 96x Dependent on Line Card Modular downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>Stackwise Virtual stacking supported for 2 switches (DNA Advantage)</t>
-  </si>
-  <si>
-    <t>C9407R</t>
-  </si>
-  <si>
-    <t>switching.csv row 239</t>
-  </si>
-  <si>
-    <t>C9400: 240x Dependent on Line Card Modular downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9410R</t>
-  </si>
-  <si>
-    <t>switching.csv row 240</t>
-  </si>
-  <si>
-    <t>C9400: 384x Dependent on Line Card Modular downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9500X-28C8D</t>
-  </si>
-  <si>
-    <t>C9500</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-9500-series-switches/series.html</t>
-  </si>
-  <si>
-    <t>core, distribution</t>
-  </si>
-  <si>
-    <t>40, 100</t>
-  </si>
-  <si>
-    <t>40, 100, 200, 400</t>
-  </si>
-  <si>
-    <t>switching.csv row 257</t>
-  </si>
-  <si>
-    <t>C9500: 36x 100G / 400G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>DNA Advantage is required for Stackwise Virtual stacking!</t>
-  </si>
-  <si>
-    <t>C9500X-60L4D</t>
-  </si>
-  <si>
-    <t>10, 25, 50</t>
-  </si>
-  <si>
-    <t>switching.csv row 258</t>
-  </si>
-  <si>
-    <t>C9500: 64x 50G / 400G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9500-32C</t>
-  </si>
-  <si>
-    <t>switching.csv row 259</t>
-  </si>
-  <si>
-    <t>C9500: 32x 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>switching.csv row 260</t>
-  </si>
-  <si>
-    <t>C9500: 32x 40G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>DNA Advantage is required for Stackwise Virtual stacking! Ports can also be used as 16x 100G</t>
-  </si>
-  <si>
-    <t>C9500-48Y4C</t>
-  </si>
-  <si>
-    <t>switching.csv row 263</t>
-  </si>
-  <si>
-    <t>C9500: 48x 25G Fiber downlinks and 4x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9500-24Y4C</t>
-  </si>
-  <si>
-    <t>switching.csv row 264</t>
-  </si>
-  <si>
-    <t>C9500: 24x 25G Fiber downlinks and 4x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9500-16X</t>
-  </si>
-  <si>
-    <t>NMs: none</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9500-series-switches/c9500-16x-switch-nm-c9500-nm-8x-nm-2q-eol.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 265</t>
-  </si>
-  <si>
-    <t>C9500: 16x 10G Fiber downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9500-16X-2Q</t>
+    <t>C9400: 12x 40G / 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9500-NM-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 246</t>
+  </si>
+  <si>
+    <t>C9500: 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9500-NM-8X</t>
+  </si>
+  <si>
+    <t>switching.csv row 247</t>
+  </si>
+  <si>
+    <t>C9500: 8x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9600-LC-24C</t>
+  </si>
+  <si>
+    <t>switching.csv row 249</t>
+  </si>
+  <si>
+    <t>C9600: 24x 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9600-LC-48YL</t>
+  </si>
+  <si>
+    <t>switching.csv row 250</t>
+  </si>
+  <si>
+    <t>C9600: 48x 25G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9600-LC-48TX</t>
+  </si>
+  <si>
+    <t>switching.csv row 251</t>
+  </si>
+  <si>
+    <t>C9600: 48x 10G Copper downlinks</t>
+  </si>
+  <si>
+    <t>C9600-LC-48S</t>
+  </si>
+  <si>
+    <t>switching.csv row 252</t>
+  </si>
+  <si>
+    <t>C9600: 48x 1G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9600-LC-40YL4CD</t>
+  </si>
+  <si>
+    <t>switching.csv row 253</t>
+  </si>
+  <si>
+    <t>C9600: 44x 25G / 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9600X-LC-56YL4C</t>
+  </si>
+  <si>
+    <t>switching.csv row 254</t>
+  </si>
+  <si>
+    <t>C9600: 60x 25G / 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9600X-LC-32CD</t>
+  </si>
+  <si>
+    <t>100, 400</t>
+  </si>
+  <si>
+    <t>switching.csv row 255</t>
+  </si>
+  <si>
+    <t>C9600: 32x 100G / 400G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9350-NM-4C</t>
   </si>
   <si>
     <t>switching.csv row 266</t>
   </si>
   <si>
-    <t>C9500: 16x 10G Fiber downlinks and 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9606R</t>
-  </si>
-  <si>
-    <t>C9600</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/td/docs/switches/lan/catalyst9600/software/release/17-12/release_notes/ol-17-12-9600/introduction.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 269</t>
-  </si>
-  <si>
-    <t>C9600: 192x Dependent on Line Card Modular downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-24T</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9000-switches/c9000-smart-switches-faq.html</t>
-  </si>
-  <si>
-    <t>25, 100</t>
-  </si>
-  <si>
-    <t>switching.csv row 277</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 24x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>AI ready hardware using Cisco Silicon One ASICs</t>
-  </si>
-  <si>
-    <t>C9350-48T</t>
-  </si>
-  <si>
-    <t>switching.csv row 278</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-24P</t>
-  </si>
-  <si>
-    <t>switching.csv row 279</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 24x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-48P</t>
-  </si>
-  <si>
-    <t>switching.csv row 280</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x PoE+ 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-24U</t>
-  </si>
-  <si>
-    <t>switching.csv row 281</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 24x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-48U</t>
-  </si>
-  <si>
-    <t>switching.csv row 282</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x UPOE 1G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-48TX</t>
-  </si>
-  <si>
-    <t>switching.csv row 283</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-24HX</t>
-  </si>
-  <si>
-    <t>switching.csv row 284</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 24x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-48HX</t>
-  </si>
-  <si>
-    <t>switching.csv row 285</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x UPOE+ 10G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9350-48HXN</t>
-  </si>
-  <si>
-    <t>switching.csv row 286</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 48x UPOE+ 5G Copper downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>C9550-24L4CD</t>
-  </si>
-  <si>
-    <t>C9550 SmartSwitch</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/networking/switches/c9550-series-smart-switches-ds.html</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>switching.csv row 290</t>
-  </si>
-  <si>
-    <t>C9550 SmartSwitch: 24 ports 50/25/10/1G downlinks, four 100/40G or two 400G ports as fixed uplinks</t>
-  </si>
-  <si>
-    <t>C9550-48L4CD</t>
-  </si>
-  <si>
-    <t>switching.csv row 291</t>
-  </si>
-  <si>
-    <t>C9550 SmartSwitch: 48 ports 50/25/10/1G downlinks, four 100/40G or two 400G ports as fixed uplinks</t>
-  </si>
-  <si>
-    <t>C9550-96L4D</t>
-  </si>
-  <si>
-    <t>switching.csv row 292</t>
-  </si>
-  <si>
-    <t>C9550 SmartSwitch: 96 ports 50/25/10/1G downlinks, four 400/100/40G ports as fixed uplinks</t>
-  </si>
-  <si>
-    <t>C9610R</t>
-  </si>
-  <si>
-    <t>C9610 SmartSwitch</t>
-  </si>
-  <si>
-    <t>switching.csv row 293</t>
-  </si>
-  <si>
-    <t>C9610 SmartSwitch: 384x Dependent on Line Card Modular downlinks and Modular uplinks</t>
-  </si>
-  <si>
-    <t>IE-1000-4T1T-LM</t>
-  </si>
-  <si>
-    <t>IE1000</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/industrial-ethernet-1000-series-switches/datasheet-c78-737277.html</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>rugged, redundant_psu, dc_power</t>
-  </si>
-  <si>
-    <t>switching.csv row 300</t>
-  </si>
-  <si>
-    <t>IE1000 with 4 FE Copper ports and 1 FE Copper uplinks, Rugged</t>
-  </si>
-  <si>
-    <t>rugged, Redundant PSU, DC Power</t>
-  </si>
-  <si>
-    <t>IE-1000-6T2T-LM</t>
-  </si>
-  <si>
-    <t>switching.csv row 301</t>
-  </si>
-  <si>
-    <t>IE1000 with 6 FE Copper ports and 2 FE Copper uplinks, Rugged</t>
-  </si>
-  <si>
-    <t>IE-1000-4P2S-LM</t>
-  </si>
-  <si>
-    <t>rugged, poe, redundant_psu, dc_power</t>
+    <t>C9350 SmartSwitch: 4x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9350-NM-2C</t>
+  </si>
+  <si>
+    <t>switching.csv row 267</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 2x 100Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9350-NM-8Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 268</t>
+  </si>
+  <si>
+    <t>C9350 SmartSwitch: 8x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9610-LC-32CD</t>
+  </si>
+  <si>
+    <t>switching.csv row 273</t>
+  </si>
+  <si>
+    <t>C9610 SmartSwitch: 32x 100G / 400G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>C9610-LC-40YL4CD</t>
+  </si>
+  <si>
+    <t>switching.csv row 274</t>
+  </si>
+  <si>
+    <t>C9610 SmartSwitch: 44x 25G / 100G Fiber downlinks</t>
+  </si>
+  <si>
+    <t>IEM-3300-8T</t>
   </si>
   <si>
     <t>switching.csv row 302</t>
   </si>
   <si>
-    <t>IE1000 with 4 FE Copper PoE+ ports and 2 GE SFP uplinks, Rugged</t>
-  </si>
-  <si>
-    <t>rugged, PoE, Redundant PSU, DC Power</t>
-  </si>
-  <si>
-    <t>IE-1000-8P2S-LM</t>
+    <t>IE3300: 8x 1G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-8P</t>
   </si>
   <si>
     <t>switching.csv row 303</t>
   </si>
   <si>
-    <t>IE1000 with 8 FE Copper PoE+ ports and 2 GE SFP uplinks, Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-4T2S</t>
-  </si>
-  <si>
-    <t>IE3100</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/networking/industrial-switches/catalyst-ie3100-rugged-series/catalyst-ie3100-rugged-series-ds.html</t>
+    <t>IE3300: 8x PoE+ 1G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-8S</t>
   </si>
   <si>
     <t>switching.csv row 304</t>
   </si>
   <si>
-    <t>IE3100: 4x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-8T2C</t>
+    <t>IE3300: 8x 1G Fiber downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-16T</t>
   </si>
   <si>
     <t>switching.csv row 305</t>
   </si>
   <si>
-    <t>IE3100: 8x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-8T4S</t>
+    <t>IE3300: 16x 1G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-16P</t>
   </si>
   <si>
     <t>switching.csv row 306</t>
   </si>
   <si>
-    <t>IE3100: 8x 1G Copper downlinks and 4x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-18T2C</t>
+    <t>IE3300: 16x PoE+ 1G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-6T2S</t>
   </si>
   <si>
     <t>switching.csv row 307</t>
   </si>
   <si>
-    <t>IE3100: 18x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-18T2C-CC</t>
+    <t>IE3300: 8x 1G Copper/ Fiber downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-14T2S</t>
   </si>
   <si>
     <t>switching.csv row 308</t>
   </si>
   <si>
-    <t>IE3100: 18x 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged, Conformal Coating</t>
-  </si>
-  <si>
-    <t>IE-3105-8T2C</t>
+    <t>IE3300: 16x 1G Copper/ Fiber downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3300-4MU</t>
   </si>
   <si>
     <t>switching.csv row 309</t>
   </si>
   <si>
-    <t>IE-3105-18T2C</t>
-  </si>
-  <si>
-    <t>switching.csv row 310</t>
-  </si>
-  <si>
-    <t>IE-3100-4P2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 311</t>
-  </si>
-  <si>
-    <t>IE3100: 4x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-3P1U2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 312</t>
-  </si>
-  <si>
-    <t>IE3100: 4x 4PPoE 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-8P2C</t>
-  </si>
-  <si>
-    <t>switching.csv row 313</t>
-  </si>
-  <si>
-    <t>IE3100: 8x PoE+ 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100-6P2U2C</t>
-  </si>
-  <si>
-    <t>switching.csv row 314</t>
-  </si>
-  <si>
-    <t>IE3100: 8x 4PPoE 1G Copper downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3100H-6FT2T-E</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/networking/industrial-switches/catalyst-ie3100-heavy-duty-series/catalyst-ie3100-heavy-duty-series-ds.html#Orderinginformation</t>
-  </si>
-  <si>
-    <t>rugged, dc_power, heavyduty</t>
-  </si>
-  <si>
-    <t>switching.csv row 315</t>
-  </si>
-  <si>
-    <t>IE3100: IP67 w/6FE 2GE M12 Ports, Rugged Heavy Duty</t>
-  </si>
-  <si>
-    <t>rugged, DC power, Heavyduty</t>
-  </si>
-  <si>
-    <t>IE-3100H-8T-E</t>
-  </si>
-  <si>
-    <t>switching.csv row 316</t>
-  </si>
-  <si>
-    <t>IE3100: IP67 w/8GE M12 Ports, Rugged Heavy Duty</t>
-  </si>
-  <si>
-    <t>IE-3200-8T2S</t>
-  </si>
-  <si>
-    <t>IE3200</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3200-rugged-series/cat-ie3200-rugged-series-ds.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 317</t>
-  </si>
-  <si>
-    <t>IE-3200: 8x 1G Copper downlinks and 2x 1G SFP Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3200-8P2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 318</t>
-  </si>
-  <si>
-    <t>IE-3200: 8x PoE+ 1G Copper downlinks and 2x 1G SFP Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3300-8P2S</t>
-  </si>
-  <si>
-    <t>IE3300</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3300-rugged-series/catalyst-ie3300-rugged-series-ds.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 319</t>
-  </si>
-  <si>
-    <t>IE3300: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>rugged, PoE, Redundant PSU, DC power</t>
-  </si>
-  <si>
-    <t>IE-3300-8U2X</t>
-  </si>
-  <si>
-    <t>switching.csv row 320</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 4PPoE 1G Copper downlinks and 2x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3300-8T2S</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-ie3300-rugged-series/series.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 321</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3300-8T2X</t>
-  </si>
-  <si>
-    <t>switching.csv row 322</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 1G Copper downlinks and 2x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3400-8T2S</t>
-  </si>
-  <si>
-    <t>IE3400</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-ie3400-rugged-series/cat-ie3400-rugged-series-ds.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 331</t>
-  </si>
-  <si>
-    <t>IE3400: 8x 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>rugged, Redundant PSU, DC power</t>
-  </si>
-  <si>
-    <t>IE-3400-8P2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 332</t>
-  </si>
-  <si>
-    <t>IE3400: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-3400H-8FT</t>
-  </si>
-  <si>
-    <t>switching.csv row 333</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 8 FE M12 interfaces, IP67</t>
-  </si>
-  <si>
-    <t>Heavy Duty industrial switch with M12 connectors</t>
-  </si>
-  <si>
-    <t>IE-3400H-16FT</t>
-  </si>
-  <si>
-    <t>switching.csv row 334</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 16 FE M12 interfaces, IP67</t>
-  </si>
-  <si>
-    <t>IE-3400H-24FT</t>
-  </si>
-  <si>
-    <t>switching.csv row 335</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 24 FE M12 interfaces, IP67</t>
-  </si>
-  <si>
-    <t>IE-3400H-8T</t>
-  </si>
-  <si>
-    <t>switching.csv row 336</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 8 GE M12 interfaces, IP67,</t>
-  </si>
-  <si>
-    <t>IE-3400H-16T</t>
-  </si>
-  <si>
-    <t>switching.csv row 337</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 16 GE M12 interfaces, IP67</t>
-  </si>
-  <si>
-    <t>IE-3400H-24T</t>
-  </si>
-  <si>
-    <t>switching.csv row 338</t>
-  </si>
-  <si>
-    <t>Catalyst IE3400 Heavy Duty w/ 24 GE M12 interfaces, IP67</t>
-  </si>
-  <si>
-    <t>IE-9310-26S2C</t>
-  </si>
-  <si>
-    <t>IE9300</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/support/switches/catalyst-ie9300-rugged-series/series.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 349</t>
-  </si>
-  <si>
-    <t>IE9300: 26x 1G Fiber downlinks and 2x 1G Copper + Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-9320-26S2C</t>
-  </si>
-  <si>
-    <t>rugged, stacking, redundant_psu, dc_power</t>
-  </si>
-  <si>
-    <t>switching.csv row 350</t>
-  </si>
-  <si>
-    <t>rugged, Stacking, Redundant PSU, DC Power</t>
-  </si>
-  <si>
-    <t>IE-9320-22S2C4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 351</t>
-  </si>
-  <si>
-    <t>IE9300: 24x 1G Fiber downlinks and 4x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-9320-24P4S</t>
-  </si>
-  <si>
-    <t>rugged, poe, stacking, redundant_psu, dc_power</t>
-  </si>
-  <si>
-    <t>switching.csv row 352</t>
-  </si>
-  <si>
-    <t>IE9300: 24x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>rugged, PoE, Stacking, Redundant PSU, DC Power</t>
-  </si>
-  <si>
-    <t>IE-9320-24T4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 353</t>
-  </si>
-  <si>
-    <t>IE9300: 24x 1G Copper downlinks and 4x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-9320-24P4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 354</t>
-  </si>
-  <si>
-    <t>IE9300: 24x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>IE-9320-16P8U4X</t>
-  </si>
-  <si>
-    <t>1, 2.5</t>
-  </si>
-  <si>
-    <t>rugged, poe, stacking, multigigabit, redundant_psu, dc_power</t>
-  </si>
-  <si>
-    <t>switching.csv row 355</t>
-  </si>
-  <si>
-    <t>IE9300: 16 ports 1G Copper PoE+ and 8 ports 2.5G 4PPoE downlinks and 4x 1/10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>rugged, PoE, Stacking, Multigigabit, Redundant PSU, DC Power</t>
-  </si>
-  <si>
-    <t>IE-9310-16P8S4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 356</t>
-  </si>
-  <si>
-    <t>IE9300: 16x PoE+ 1G Copper and 8x 1G Fiber downlinks and 4x 10G Fiber uplinks Rugged</t>
-  </si>
-  <si>
-    <t>CBS220-8T-E-2G</t>
-  </si>
-  <si>
-    <t>CBS220</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/small-business-220-series-smart-plus-switches/220-series-smart-switches-eol.html</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/switches/cisco-business-switches/index.html</t>
-  </si>
-  <si>
-    <t>smart_managed, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 357</t>
-  </si>
-  <si>
-    <t>CBS220: 8x 1G Copper downlinks and 2x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>smart managed, SMB</t>
-  </si>
-  <si>
-    <t>CBS220-8P-E-2G</t>
-  </si>
-  <si>
-    <t>smart_managed, poe, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 358</t>
-  </si>
-  <si>
-    <t>CBS220: 8x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>smart managed, PoE, SMB</t>
-  </si>
-  <si>
-    <t>CBS220-8FP-E-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 359</t>
-  </si>
-  <si>
-    <t>CBS220: 8x PoE+ (Full) 1G Copper downlinks and 2x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-16T-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 360</t>
-  </si>
-  <si>
-    <t>CBS220: 16x 1G Copper downlinks and 2x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-16P-2G</t>
-  </si>
-  <si>
-    <t>switching.csv row 361</t>
-  </si>
-  <si>
-    <t>CBS220: 16x PoE+ 1G Copper downlinks and 2x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 362</t>
-  </si>
-  <si>
-    <t>CBS220: 24x 1G Copper downlinks and 4x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 363</t>
-  </si>
-  <si>
-    <t>CBS220: 24x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24FP-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 364</t>
-  </si>
-  <si>
-    <t>CBS220: 24x PoE+ (Full) 1G Copper downlinks and 4x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-48T-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 365</t>
-  </si>
-  <si>
-    <t>CBS220: 48x 1G Copper downlinks and 4x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-48P-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 366</t>
-  </si>
-  <si>
-    <t>CBS220: 48x PoE+ 1G Copper downlinks and 4x 1G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 367</t>
-  </si>
-  <si>
-    <t>CBS220: 24x 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 368</t>
-  </si>
-  <si>
-    <t>CBS220: 24x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-24FP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 369</t>
-  </si>
-  <si>
-    <t>CBS220: 24x PoE+ (Full) 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-48T-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 370</t>
-  </si>
-  <si>
-    <t>CBS220: 48x 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-48P-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 371</t>
-  </si>
-  <si>
-    <t>CBS220: 48x PoE+ 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS220-48FP-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 372</t>
-  </si>
-  <si>
-    <t>CBS220: 48x PoE+ (Full) 1G Copper downlinks and 4x 10G Fiber uplinks</t>
-  </si>
-  <si>
-    <t>CBS110-5T-D</t>
-  </si>
-  <si>
-    <t>CBS110</t>
-  </si>
-  <si>
-    <t>unmanaged, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 373</t>
-  </si>
-  <si>
-    <t>CBS110: 5x 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>Unmanaged</t>
-  </si>
-  <si>
-    <t>unmanaged, SMB</t>
-  </si>
-  <si>
-    <t>CBS110-8T-D</t>
-  </si>
-  <si>
-    <t>switching.csv row 374</t>
-  </si>
-  <si>
-    <t>CBS110: 8x 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>CBS110-8PP-D</t>
-  </si>
-  <si>
-    <t>unmanaged, poe, smb</t>
-  </si>
-  <si>
-    <t>switching.csv row 375</t>
-  </si>
-  <si>
-    <t>CBS110: 8x PoE (Partial) 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>unmanaged, PoE, SMB</t>
-  </si>
-  <si>
-    <t>CBS110-16T</t>
-  </si>
-  <si>
-    <t>switching.csv row 376</t>
-  </si>
-  <si>
-    <t>CBS110: 16x 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>CBS110-16PP</t>
-  </si>
-  <si>
-    <t>switching.csv row 377</t>
-  </si>
-  <si>
-    <t>CBS110: 16x PoE (Partial) 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>CBS110-24T</t>
-  </si>
-  <si>
-    <t>switching.csv row 378</t>
-  </si>
-  <si>
-    <t>CBS110: 24x 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>CBS110-24PP</t>
-  </si>
-  <si>
-    <t>switching.csv row 379</t>
-  </si>
-  <si>
-    <t>CBS110: 24x PoE (Partial) 1G Copper downlinks Unmanaged</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>speed_gbps</t>
-  </si>
-  <si>
-    <t>C9300-NM-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 76</t>
-  </si>
-  <si>
-    <t>9300-M: 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-8X</t>
-  </si>
-  <si>
-    <t>switching.csv row 77</t>
-  </si>
-  <si>
-    <t>9300-M: 8x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 78</t>
-  </si>
-  <si>
-    <t>9300-M: 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-2Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 79</t>
-  </si>
-  <si>
-    <t>9300-M: 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-4M</t>
-  </si>
-  <si>
-    <t>switching.csv row 80</t>
-  </si>
-  <si>
-    <t>9300-M: 4x 10Gbps Multigigabit Copper uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-BLANK</t>
-  </si>
-  <si>
-    <t>switching.csv row 81</t>
-  </si>
-  <si>
-    <t>C9300X-NM-8M</t>
-  </si>
-  <si>
-    <t>switching.csv row 95</t>
-  </si>
-  <si>
-    <t>9300X-M: 8x 10Gbps Multigigabit Copper uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-NM-8Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 96</t>
-  </si>
-  <si>
-    <t>9300X-M: 8x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-NM-2C</t>
-  </si>
-  <si>
-    <t>switching.csv row 97</t>
-  </si>
-  <si>
-    <t>9300X-M: 2x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-NM-4C</t>
-  </si>
-  <si>
-    <t>switching.csv row 98</t>
-  </si>
-  <si>
-    <t>9300X-M: 4x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300X-NM-BLANK</t>
-  </si>
-  <si>
-    <t>switching.csv row 99</t>
-  </si>
-  <si>
-    <t>C9200-NM-2Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 161</t>
-  </si>
-  <si>
-    <t>C9200: 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 162</t>
-  </si>
-  <si>
-    <t>C9200: 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 163</t>
-  </si>
-  <si>
-    <t>C9200: 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 164</t>
-  </si>
-  <si>
-    <t>C9200: 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-BLANK</t>
-  </si>
-  <si>
-    <t>switching.csv row 165</t>
-  </si>
-  <si>
-    <t>BLANK</t>
-  </si>
-  <si>
-    <t>switching.csv row 208</t>
-  </si>
-  <si>
-    <t>C9400-SUP-1</t>
-  </si>
-  <si>
-    <t>fiber, hybrid</t>
-  </si>
-  <si>
-    <t>2025-04-30</t>
-  </si>
-  <si>
-    <t>2030-04-30</t>
-  </si>
-  <si>
-    <t>C9400X-SUP-2 / C9400X-SUP-2XL</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/catalyst-9400-series-switches/catalyst-9400-series-supervisor-module-eol.html</t>
-  </si>
-  <si>
-    <t>switching.csv row 241</t>
-  </si>
-  <si>
-    <t>C9400: 8x 10Gbps / 40Gbps Fiber / Hybrid uplinks</t>
-  </si>
-  <si>
-    <t>C9400-SUP-1XL</t>
-  </si>
-  <si>
-    <t>switching.csv row 242</t>
-  </si>
-  <si>
-    <t>C9400-LC-48U</t>
-  </si>
-  <si>
-    <t>switching.csv row 243</t>
-  </si>
-  <si>
-    <t>C9400: 48x UPOE 1G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48P</t>
-  </si>
-  <si>
-    <t>switching.csv row 244</t>
-  </si>
-  <si>
-    <t>C9400: 48x PoE+ 1G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48T</t>
-  </si>
-  <si>
-    <t>switching.csv row 245</t>
-  </si>
-  <si>
-    <t>C9400: 48x 1G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48UX</t>
-  </si>
-  <si>
-    <t>switching.csv row 246</t>
-  </si>
-  <si>
-    <t>C9400: 48x UPOE 10G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-24XS</t>
-  </si>
-  <si>
-    <t>switching.csv row 247</t>
-  </si>
-  <si>
-    <t>C9400: 24x 10G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-24S</t>
-  </si>
-  <si>
-    <t>switching.csv row 248</t>
-  </si>
-  <si>
-    <t>C9400: 24x 1G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48S</t>
-  </si>
-  <si>
-    <t>switching.csv row 249</t>
-  </si>
-  <si>
-    <t>C9400: 48x 1G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48H</t>
-  </si>
-  <si>
-    <t>switching.csv row 250</t>
-  </si>
-  <si>
-    <t>C9400: 48x UPOE+ 1G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48HN</t>
-  </si>
-  <si>
-    <t>switching.csv row 251</t>
-  </si>
-  <si>
-    <t>C9400: 48x UPOE+ 5G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48HX</t>
-  </si>
-  <si>
-    <t>switching.csv row 252</t>
-  </si>
-  <si>
-    <t>C9400: 48x UPOE+ 10G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48TX</t>
-  </si>
-  <si>
-    <t>switching.csv row 253</t>
-  </si>
-  <si>
-    <t>C9400: 48x 10G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-48XS</t>
-  </si>
-  <si>
-    <t>switching.csv row 254</t>
-  </si>
-  <si>
-    <t>C9400: 48x 10G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-24XY</t>
-  </si>
-  <si>
-    <t>switching.csv row 255</t>
-  </si>
-  <si>
-    <t>C9400: 24x 25G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9400-LC-12QC</t>
-  </si>
-  <si>
-    <t>switching.csv row 256</t>
-  </si>
-  <si>
-    <t>C9400: 12x 40G / 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9500-NM-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 267</t>
-  </si>
-  <si>
-    <t>C9500: 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9500-NM-8X</t>
-  </si>
-  <si>
-    <t>switching.csv row 268</t>
-  </si>
-  <si>
-    <t>C9500: 8x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9600-LC-24C</t>
-  </si>
-  <si>
-    <t>switching.csv row 270</t>
-  </si>
-  <si>
-    <t>C9600: 24x 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9600-LC-48YL</t>
-  </si>
-  <si>
-    <t>switching.csv row 271</t>
-  </si>
-  <si>
-    <t>C9600: 48x 25G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9600-LC-48TX</t>
-  </si>
-  <si>
-    <t>switching.csv row 272</t>
-  </si>
-  <si>
-    <t>C9600: 48x 10G Copper downlinks</t>
-  </si>
-  <si>
-    <t>C9600-LC-48S</t>
-  </si>
-  <si>
-    <t>switching.csv row 273</t>
-  </si>
-  <si>
-    <t>C9600: 48x 1G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9600-LC-40YL4CD</t>
-  </si>
-  <si>
-    <t>switching.csv row 274</t>
-  </si>
-  <si>
-    <t>C9600: 44x 25G / 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9600X-LC-56YL4C</t>
-  </si>
-  <si>
-    <t>switching.csv row 275</t>
-  </si>
-  <si>
-    <t>C9600: 60x 25G / 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9600X-LC-32CD</t>
-  </si>
-  <si>
-    <t>100, 400</t>
-  </si>
-  <si>
-    <t>switching.csv row 276</t>
-  </si>
-  <si>
-    <t>C9600: 32x 100G / 400G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9350-NM-4C</t>
-  </si>
-  <si>
-    <t>switching.csv row 287</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 4x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9350-NM-2C</t>
-  </si>
-  <si>
-    <t>switching.csv row 288</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 2x 100Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9350-NM-8Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 289</t>
-  </si>
-  <si>
-    <t>C9350 SmartSwitch: 8x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9610-LC-32CD</t>
-  </si>
-  <si>
-    <t>switching.csv row 294</t>
-  </si>
-  <si>
-    <t>C9610 SmartSwitch: 32x 100G / 400G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>C9610-LC-40YL4CD</t>
-  </si>
-  <si>
-    <t>switching.csv row 295</t>
-  </si>
-  <si>
-    <t>C9610 SmartSwitch: 44x 25G / 100G Fiber downlinks</t>
-  </si>
-  <si>
-    <t>IEM-3300-8T</t>
-  </si>
-  <si>
-    <t>switching.csv row 323</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 1G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-8P</t>
-  </si>
-  <si>
-    <t>switching.csv row 324</t>
-  </si>
-  <si>
-    <t>IE3300: 8x PoE+ 1G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-8S</t>
-  </si>
-  <si>
-    <t>switching.csv row 325</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 1G Fiber downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-16T</t>
+    <t>IE3300: 4x 4PPoE 2.5G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3400-8T</t>
   </si>
   <si>
     <t>switching.csv row 326</t>
   </si>
   <si>
-    <t>IE3300: 16x 1G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-16P</t>
+    <t>IE3400: 8x 1G Copper downlinks Rugged</t>
+  </si>
+  <si>
+    <t>IEM-3400-8S</t>
   </si>
   <si>
     <t>switching.csv row 327</t>
-  </si>
-  <si>
-    <t>IE3300: 16x PoE+ 1G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-6T2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 328</t>
-  </si>
-  <si>
-    <t>IE3300: 8x 1G Copper/ Fiber downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-14T2S</t>
-  </si>
-  <si>
-    <t>switching.csv row 329</t>
-  </si>
-  <si>
-    <t>IE3300: 16x 1G Copper/ Fiber downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3300-4MU</t>
-  </si>
-  <si>
-    <t>switching.csv row 330</t>
-  </si>
-  <si>
-    <t>IE3300: 4x 4PPoE 2.5G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3400-8T</t>
-  </si>
-  <si>
-    <t>switching.csv row 347</t>
-  </si>
-  <si>
-    <t>IE3400: 8x 1G Copper downlinks Rugged</t>
-  </si>
-  <si>
-    <t>IEM-3400-8S</t>
-  </si>
-  <si>
-    <t>switching.csv row 348</t>
   </si>
   <si>
     <t>IE3400: 8x 1G Fiber downlinks Rugged</t>

--- a/data/catalog/switching.xlsx
+++ b/data/catalog/switching.xlsx
@@ -1565,7 +1565,7 @@
     <t>2031-10-31</t>
   </si>
   <si>
-    <t>Cisco'nun önerdiği yedek: Catalyst 9500 (C9500-32QC).</t>
+    <t>Cisco'nun önerdiği yedek: Catalyst 9500 serisi (henüz kataloğa eklenmedi).</t>
   </si>
   <si>
     <t>https://www.cisco.com/c/en/us/products/collateral/networking/switches/meraki-switches/meraki-ms450-12x40g-aggregation-switch-eol.html</t>
@@ -6536,10 +6536,10 @@
     <t>MS210: end of sale was 30 April 2026; Meraki recommends the MS150. Do not use it in new projects; it is listed only to recognise installed devices.</t>
   </si>
   <si>
-    <t>MS450: 12 x 40G toplama anahtarı. Satışı sona eriyor (son sipariş 29 Ekim 2026); yerine Catalyst 9500 (C9500-32QC) önerilir.</t>
-  </si>
-  <si>
-    <t>MS450: a 12 x 40G aggregation switch. End of sale is announced (last order 29 October 2026); the Catalyst 9500 (C9500-32QC) is the suggested replacement.</t>
+    <t>MS450: 12 x 40G toplama anahtarı. Satışı sona eriyor (son sipariş 29 Ekim 2026); yerine Catalyst 9500 serisi önerilir.</t>
+  </si>
+  <si>
+    <t>MS450: a 12 x 40G aggregation switch. End of sale is announced (last order 29 October 2026); the Catalyst 9500 series is the suggested replacement.</t>
   </si>
 </sst>
 </file>

--- a/data/catalog/switching.xlsx
+++ b/data/catalog/switching.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12168" uniqueCount="2175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11913" uniqueCount="2176">
   <si>
     <t>family</t>
   </si>
@@ -5849,54 +5849,54 @@
     <t>C9300-NM-4G</t>
   </si>
   <si>
+    <t>switching.csv row 57</t>
+  </si>
+  <si>
+    <t>9300-M: 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-8X</t>
+  </si>
+  <si>
+    <t>switching.csv row 58</t>
+  </si>
+  <si>
+    <t>9300-M: 8x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 59</t>
+  </si>
+  <si>
+    <t>9300-M: 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-2Y</t>
+  </si>
+  <si>
+    <t>switching.csv row 60</t>
+  </si>
+  <si>
+    <t>9300-M: 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-4M</t>
+  </si>
+  <si>
+    <t>switching.csv row 61</t>
+  </si>
+  <si>
+    <t>9300-M: 4x 10Gbps Multigigabit Copper uplinks</t>
+  </si>
+  <si>
+    <t>C9300-NM-BLANK</t>
+  </si>
+  <si>
     <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9300-series-switches/datasheet-listing.html</t>
   </si>
   <si>
-    <t>switching.csv row 57</t>
-  </si>
-  <si>
-    <t>9300-M: 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-8X</t>
-  </si>
-  <si>
-    <t>switching.csv row 58</t>
-  </si>
-  <si>
-    <t>9300-M: 8x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 59</t>
-  </si>
-  <si>
-    <t>9300-M: 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-2Y</t>
-  </si>
-  <si>
-    <t>switching.csv row 60</t>
-  </si>
-  <si>
-    <t>9300-M: 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-4M</t>
-  </si>
-  <si>
-    <t>switching.csv row 61</t>
-  </si>
-  <si>
-    <t>9300-M: 4x 10Gbps Multigigabit Copper uplinks</t>
-  </si>
-  <si>
-    <t>C9300-NM-BLANK</t>
-  </si>
-  <si>
     <t>switching.csv row 62</t>
   </si>
   <si>
@@ -5945,45 +5945,45 @@
     <t>C9200-NM-2Y</t>
   </si>
   <si>
+    <t>switching.csv row 142</t>
+  </si>
+  <si>
+    <t>C9200: 2x 25Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-2Q</t>
+  </si>
+  <si>
+    <t>switching.csv row 143</t>
+  </si>
+  <si>
+    <t>C9200: 2x 40Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-4G</t>
+  </si>
+  <si>
+    <t>switching.csv row 144</t>
+  </si>
+  <si>
+    <t>C9200: 4x 1Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-4X</t>
+  </si>
+  <si>
+    <t>switching.csv row 145</t>
+  </si>
+  <si>
+    <t>C9200: 4x 10Gbps Fiber uplinks</t>
+  </si>
+  <si>
+    <t>C9200-NM-BLANK</t>
+  </si>
+  <si>
     <t>https://www.cisco.com/c/en/us/products/switches/catalyst-9200-series-switches/datasheet-listing.html</t>
   </si>
   <si>
-    <t>switching.csv row 142</t>
-  </si>
-  <si>
-    <t>C9200: 2x 25Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-2Q</t>
-  </si>
-  <si>
-    <t>switching.csv row 143</t>
-  </si>
-  <si>
-    <t>C9200: 2x 40Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-4G</t>
-  </si>
-  <si>
-    <t>switching.csv row 144</t>
-  </si>
-  <si>
-    <t>C9200: 4x 1Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-4X</t>
-  </si>
-  <si>
-    <t>switching.csv row 145</t>
-  </si>
-  <si>
-    <t>C9200: 4x 10Gbps Fiber uplinks</t>
-  </si>
-  <si>
-    <t>C9200-NM-BLANK</t>
-  </si>
-  <si>
     <t>switching.csv row 146</t>
   </si>
   <si>
@@ -6377,18 +6377,18 @@
     <t>legacy series grouping (Meraki / 9300-M)</t>
   </si>
   <si>
+    <t>legacy series grouping (Meraki / 9300X-M)</t>
+  </si>
+  <si>
+    <t>legacy series grouping (Catalyst / C9200)</t>
+  </si>
+  <si>
+    <t>legacy series grouping (Catalyst / C9300X)</t>
+  </si>
+  <si>
     <t>legacy series grouping (Catalyst / C9300)</t>
   </si>
   <si>
-    <t>legacy series grouping (Meraki / 9300X-M)</t>
-  </si>
-  <si>
-    <t>legacy series grouping (Catalyst / C9300X)</t>
-  </si>
-  <si>
-    <t>legacy series grouping (Catalyst / C9200)</t>
-  </si>
-  <si>
     <t>legacy series grouping (Catalyst / C9400)</t>
   </si>
   <si>
@@ -6408,6 +6408,9 @@
   </si>
   <si>
     <t>legacy series grouping (Catalyst / IE3400)</t>
+  </si>
+  <si>
+    <t>Cisco data sheet, 13 Oct 2026</t>
   </si>
   <si>
     <t>series_intro_tr</t>
@@ -43559,7 +43562,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -43578,6 +43581,9 @@
       </c>
       <c r="J2" t="s">
         <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -43586,28 +43592,32 @@
       <c r="P2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>1944</v>
       </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>1945</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>1946</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>628</v>
       </c>
       <c r="Z2" s="1"/>
-      <c r="AA2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -43616,16 +43626,16 @@
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -43635,6 +43645,9 @@
       </c>
       <c r="J3" t="s">
         <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -43643,28 +43656,32 @@
       <c r="P3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W3" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>1948</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>1949</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>628</v>
       </c>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -43673,16 +43690,16 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -43692,6 +43709,9 @@
       </c>
       <c r="J4" t="s">
         <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -43700,28 +43720,32 @@
       <c r="P4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W4" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>1951</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>1952</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>628</v>
       </c>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA4" s="1"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -43730,16 +43754,16 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -43749,6 +43773,9 @@
       </c>
       <c r="J5" t="s">
         <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -43757,28 +43784,32 @@
       <c r="P5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W5" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>1954</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>1955</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>628</v>
       </c>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -43787,16 +43818,16 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -43806,6 +43837,9 @@
       </c>
       <c r="J6" t="s">
         <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -43814,28 +43848,32 @@
       <c r="P6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W6" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>1957</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>1958</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>628</v>
       </c>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -43850,10 +43888,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -43862,7 +43900,7 @@
       <c r="P7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>1944</v>
+        <v>1959</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -43890,7 +43928,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -43909,6 +43947,9 @@
       </c>
       <c r="J8" t="s">
         <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -43917,11 +43958,17 @@
       <c r="P8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W8" s="1" t="s">
         <v>1962</v>
       </c>
@@ -43930,9 +43977,7 @@
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -43945,7 +43990,7 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -43964,6 +44009,9 @@
       </c>
       <c r="J9" t="s">
         <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -43972,11 +44020,17 @@
       <c r="P9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W9" s="1" t="s">
         <v>1965</v>
       </c>
@@ -43985,9 +44039,7 @@
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA9" s="1"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -44000,7 +44052,7 @@
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -44019,6 +44071,9 @@
       </c>
       <c r="J10" t="s">
         <v>57</v>
+      </c>
+      <c r="K10" t="s">
+        <v>29</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -44027,11 +44082,17 @@
       <c r="P10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W10" s="1" t="s">
         <v>1968</v>
       </c>
@@ -44040,9 +44101,7 @@
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -44055,7 +44114,7 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -44074,6 +44133,9 @@
       </c>
       <c r="J11" t="s">
         <v>57</v>
+      </c>
+      <c r="K11" t="s">
+        <v>29</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -44082,11 +44144,17 @@
       <c r="P11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W11" s="1" t="s">
         <v>1971</v>
       </c>
@@ -44095,9 +44163,7 @@
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -44131,7 +44197,7 @@
       <c r="P12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1" t="s">
-        <v>1944</v>
+        <v>1959</v>
       </c>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -44157,7 +44223,7 @@
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -44176,6 +44242,9 @@
       </c>
       <c r="J13" t="s">
         <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>29</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -44184,26 +44253,30 @@
       <c r="P13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>1976</v>
       </c>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>1977</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>1978</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
@@ -44212,16 +44285,16 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -44231,6 +44304,9 @@
       </c>
       <c r="J14" t="s">
         <v>57</v>
+      </c>
+      <c r="K14" t="s">
+        <v>29</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -44239,26 +44315,30 @@
       <c r="P14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1" t="s">
-        <v>1976</v>
-      </c>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
+        <v>1130</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W14" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="X14" s="1" t="s">
         <v>1980</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>1981</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -44267,16 +44347,16 @@
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -44286,6 +44366,9 @@
       </c>
       <c r="J15" t="s">
         <v>57</v>
+      </c>
+      <c r="K15" t="s">
+        <v>29</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -44294,26 +44377,30 @@
       <c r="P15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1" t="s">
-        <v>1976</v>
-      </c>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
+        <v>1130</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W15" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>1983</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>1984</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -44322,16 +44409,16 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -44341,6 +44428,9 @@
       </c>
       <c r="J16" t="s">
         <v>57</v>
+      </c>
+      <c r="K16" t="s">
+        <v>29</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -44349,26 +44439,30 @@
       <c r="P16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1" t="s">
-        <v>1976</v>
-      </c>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
+        <v>1130</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="W16" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>1986</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>1987</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -44383,10 +44477,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -44398,7 +44492,7 @@
       <c r="P17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1" t="s">
-        <v>1976</v>
+        <v>1988</v>
       </c>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -44445,7 +44539,7 @@
       <c r="P18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1" t="s">
-        <v>1944</v>
+        <v>1959</v>
       </c>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -46727,7 +46821,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C413"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="24" style="1" customWidth="1"/>
@@ -46747,7 +46841,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>617</v>
@@ -46758,7 +46852,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>630</v>
@@ -46769,7 +46863,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>643</v>
@@ -46780,7 +46874,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>652</v>
@@ -46791,7 +46885,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>657</v>
@@ -46802,7 +46896,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>666</v>
@@ -46813,7 +46907,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>675</v>
@@ -46824,7 +46918,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>686</v>
@@ -46835,7 +46929,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>695</v>
@@ -46846,7 +46940,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>704</v>
@@ -46857,7 +46951,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>707</v>
@@ -46868,10 +46962,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1303</v>
+        <v>768</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2120</v>
@@ -46879,10 +46973,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1314</v>
+        <v>780</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2120</v>
@@ -46890,10 +46984,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1321</v>
+        <v>791</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2120</v>
@@ -46901,10 +46995,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1328</v>
+        <v>800</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2120</v>
@@ -46912,10 +47006,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1330</v>
+        <v>809</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2120</v>
@@ -46923,10 +47017,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1337</v>
+        <v>814</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2120</v>
@@ -46934,4347 +47028,3269 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1344</v>
+        <v>1120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1346</v>
+        <v>1134</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1351</v>
+        <v>1143</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1360</v>
+        <v>1145</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1367</v>
+        <v>1150</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1369</v>
+        <v>1155</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1376</v>
+        <v>1162</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1383</v>
+        <v>1166</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>1943</v>
+        <v>1987</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1390</v>
+        <v>1168</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>1943</v>
+        <v>1990</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1393</v>
+        <v>1504</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>617</v>
+        <v>1512</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>630</v>
+        <v>1519</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>643</v>
+        <v>1526</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>652</v>
+        <v>1535</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>657</v>
+        <v>1540</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>666</v>
+        <v>1303</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>675</v>
+        <v>1314</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>686</v>
+        <v>1321</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>695</v>
+        <v>1328</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>704</v>
+        <v>1330</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>707</v>
+        <v>1337</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1303</v>
+        <v>1344</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1314</v>
+        <v>1346</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1321</v>
+        <v>1351</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1328</v>
+        <v>1360</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1330</v>
+        <v>1367</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1337</v>
+        <v>1369</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1344</v>
+        <v>1376</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1346</v>
+        <v>1383</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1351</v>
+        <v>1390</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>1947</v>
+        <v>1990</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1360</v>
+        <v>1393</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1367</v>
+        <v>1545</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1369</v>
+        <v>1554</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1376</v>
+        <v>1557</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>1947</v>
+        <v>1999</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1383</v>
+        <v>1545</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>1947</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1390</v>
+        <v>1554</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>1947</v>
+        <v>1999</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1393</v>
+        <v>1557</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>617</v>
+        <v>1545</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>630</v>
+        <v>1554</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>643</v>
+        <v>1557</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>1950</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>652</v>
+        <v>1545</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>1950</v>
+        <v>2004</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>657</v>
+        <v>1554</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>1950</v>
+        <v>2004</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>666</v>
+        <v>1557</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>1950</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>675</v>
+        <v>1545</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>1950</v>
+        <v>2007</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>686</v>
+        <v>1554</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1950</v>
+        <v>2007</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>695</v>
+        <v>1557</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>704</v>
+        <v>1545</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>707</v>
+        <v>1554</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1303</v>
+        <v>1557</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>1950</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1314</v>
+        <v>1545</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>1950</v>
+        <v>2013</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1321</v>
+        <v>1554</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>1950</v>
+        <v>2013</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1328</v>
+        <v>1557</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1950</v>
+        <v>2016</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1330</v>
+        <v>1545</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>1950</v>
+        <v>2016</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1337</v>
+        <v>1554</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>1950</v>
+        <v>2016</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1344</v>
+        <v>1557</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>1950</v>
+        <v>2019</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1346</v>
+        <v>1545</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>1950</v>
+        <v>2019</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1351</v>
+        <v>1554</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>1950</v>
+        <v>2019</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1360</v>
+        <v>1557</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>1950</v>
+        <v>2022</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1367</v>
+        <v>1545</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>1950</v>
+        <v>2022</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1369</v>
+        <v>1554</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>1950</v>
+        <v>2022</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1376</v>
+        <v>1557</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>1950</v>
+        <v>2025</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1383</v>
+        <v>1545</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>1950</v>
+        <v>2025</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1390</v>
+        <v>1554</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>1950</v>
+        <v>2025</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1393</v>
+        <v>1557</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>1953</v>
+        <v>2028</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>617</v>
+        <v>1545</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>1953</v>
+        <v>2028</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>630</v>
+        <v>1554</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>1953</v>
+        <v>2028</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>643</v>
+        <v>1557</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1953</v>
+        <v>2031</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>652</v>
+        <v>1545</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>1953</v>
+        <v>2031</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>657</v>
+        <v>1554</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>1953</v>
+        <v>2031</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>666</v>
+        <v>1557</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>1953</v>
+        <v>2034</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>675</v>
+        <v>1545</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>1953</v>
+        <v>2034</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>686</v>
+        <v>1554</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1953</v>
+        <v>2034</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>695</v>
+        <v>1557</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>1953</v>
+        <v>2037</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>704</v>
+        <v>1545</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>1953</v>
+        <v>2037</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>707</v>
+        <v>1554</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>1953</v>
+        <v>2037</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1303</v>
+        <v>1557</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>1953</v>
+        <v>2040</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1314</v>
+        <v>1545</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>1953</v>
+        <v>2040</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1321</v>
+        <v>1554</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>1953</v>
+        <v>2040</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1328</v>
+        <v>1557</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>1953</v>
+        <v>2043</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1330</v>
+        <v>1594</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>1953</v>
+        <v>2046</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1337</v>
+        <v>1594</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>1953</v>
+        <v>2049</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1344</v>
+        <v>1608</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>1953</v>
+        <v>2052</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1346</v>
+        <v>1608</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>1953</v>
+        <v>2055</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1351</v>
+        <v>1608</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>1953</v>
+        <v>2055</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1360</v>
+        <v>1664</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>2120</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>1953</v>
+        <v>2058</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1367</v>
+        <v>1608</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>1953</v>
+        <v>2061</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1369</v>
+        <v>1608</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>1953</v>
+        <v>2061</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1376</v>
+        <v>1664</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>2120</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>1953</v>
+        <v>2064</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1383</v>
+        <v>1608</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>1953</v>
+        <v>2064</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1390</v>
+        <v>1664</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>2120</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>1953</v>
+        <v>2067</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1393</v>
+        <v>1608</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>1956</v>
+        <v>2067</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>617</v>
+        <v>1664</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>2119</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>630</v>
+        <v>1613</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>643</v>
+        <v>1621</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>652</v>
+        <v>1624</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>657</v>
+        <v>1628</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>666</v>
+        <v>1631</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>675</v>
+        <v>1634</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>686</v>
+        <v>1637</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>695</v>
+        <v>1641</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>704</v>
+        <v>1645</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>1956</v>
+        <v>2071</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>707</v>
+        <v>1648</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1303</v>
+        <v>1613</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>1314</v>
+        <v>1621</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>1321</v>
+        <v>1624</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>1328</v>
+        <v>1628</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>1330</v>
+        <v>1631</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>1337</v>
+        <v>1634</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>1344</v>
+        <v>1637</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1346</v>
+        <v>1641</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1351</v>
+        <v>1645</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>1956</v>
+        <v>2074</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1360</v>
+        <v>1648</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1367</v>
+        <v>1613</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1369</v>
+        <v>1621</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1376</v>
+        <v>1624</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1383</v>
+        <v>1628</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1390</v>
+        <v>1631</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>1956</v>
+        <v>2077</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1393</v>
+        <v>1634</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>1959</v>
+        <v>2077</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>617</v>
+        <v>1637</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>1959</v>
+        <v>2077</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>630</v>
+        <v>1641</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>1959</v>
+        <v>2077</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>643</v>
+        <v>1645</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>1959</v>
+        <v>2077</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>652</v>
+        <v>1648</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>1959</v>
+        <v>2080</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>657</v>
+        <v>1664</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>2119</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>1959</v>
+        <v>2083</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>666</v>
+        <v>1664</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>2119</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>1959</v>
+        <v>2086</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>675</v>
+        <v>1737</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>1959</v>
+        <v>2086</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>686</v>
+        <v>1743</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>1959</v>
+        <v>2086</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>695</v>
+        <v>1746</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>1959</v>
+        <v>2086</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>704</v>
+        <v>1750</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>1959</v>
+        <v>2086</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>707</v>
+        <v>1753</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>2119</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>1961</v>
+        <v>2086</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>768</v>
+        <v>1759</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>780</v>
+        <v>1737</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>791</v>
+        <v>1743</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>800</v>
+        <v>1746</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>809</v>
+        <v>1750</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>814</v>
+        <v>1753</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>1961</v>
+        <v>2089</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1504</v>
+        <v>1759</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>1961</v>
+        <v>2092</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1512</v>
+        <v>1737</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>1961</v>
+        <v>2092</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1519</v>
+        <v>1743</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>1961</v>
+        <v>2092</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1526</v>
+        <v>1746</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>1961</v>
+        <v>2092</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1535</v>
+        <v>1750</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>1961</v>
+        <v>2092</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1540</v>
+        <v>1753</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>1964</v>
+        <v>2092</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>768</v>
+        <v>1759</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>780</v>
+        <v>1737</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>791</v>
+        <v>1743</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>800</v>
+        <v>1746</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>809</v>
+        <v>1750</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>814</v>
+        <v>1753</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>1964</v>
+        <v>2095</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1504</v>
+        <v>1759</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>1964</v>
+        <v>2098</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1512</v>
+        <v>1737</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>1964</v>
+        <v>2098</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>1519</v>
+        <v>1743</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>1964</v>
+        <v>2098</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>1526</v>
+        <v>1746</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>1964</v>
+        <v>2098</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1535</v>
+        <v>1750</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>1964</v>
+        <v>2098</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1540</v>
+        <v>1753</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1967</v>
+        <v>2098</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>768</v>
+        <v>1759</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>780</v>
+        <v>1737</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>791</v>
+        <v>1743</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>800</v>
+        <v>1746</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>809</v>
+        <v>1750</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>814</v>
+        <v>1753</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>1967</v>
+        <v>2101</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1504</v>
+        <v>1759</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>1967</v>
+        <v>2104</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>1512</v>
+        <v>1737</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>1967</v>
+        <v>2104</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1519</v>
+        <v>1743</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>1967</v>
+        <v>2104</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1526</v>
+        <v>1746</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>1967</v>
+        <v>2104</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1535</v>
+        <v>1750</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>2122</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>1967</v>
+        <v>2104</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1540</v>
+        <v>1753</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>1970</v>
+        <v>2104</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>768</v>
+        <v>1759</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>780</v>
+        <v>1737</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>791</v>
+        <v>1743</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>800</v>
+        <v>1746</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>809</v>
+        <v>1750</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>814</v>
+        <v>1753</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>1970</v>
+        <v>2107</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1504</v>
+        <v>1759</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>1970</v>
+        <v>2110</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1512</v>
+        <v>1753</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>1970</v>
+        <v>2110</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1519</v>
+        <v>1759</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>1970</v>
+        <v>2113</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1526</v>
+        <v>1753</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>1970</v>
+        <v>2113</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1535</v>
+        <v>1759</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>1970</v>
+        <v>1943</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1540</v>
+        <v>1303</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>768</v>
+        <v>1314</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>780</v>
+        <v>1321</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>791</v>
+        <v>1328</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>800</v>
+        <v>1330</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>809</v>
+        <v>1337</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>1973</v>
+        <v>1943</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>814</v>
+        <v>1344</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1120</v>
+        <v>1346</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1134</v>
+        <v>1351</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1143</v>
+        <v>1360</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1145</v>
+        <v>1367</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1150</v>
+        <v>1369</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1155</v>
+        <v>1376</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1162</v>
+        <v>1383</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1166</v>
+        <v>1390</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1168</v>
+        <v>1393</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1120</v>
+        <v>1303</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1134</v>
+        <v>1314</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1143</v>
+        <v>1321</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1145</v>
+        <v>1328</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1150</v>
+        <v>1330</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>1155</v>
+        <v>1337</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1162</v>
+        <v>1344</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1166</v>
+        <v>1346</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1168</v>
+        <v>1351</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1120</v>
+        <v>1360</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>1134</v>
+        <v>1367</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>1143</v>
+        <v>1369</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1145</v>
+        <v>1376</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>1150</v>
+        <v>1383</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>1155</v>
+        <v>1390</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>1982</v>
+        <v>1955</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>1162</v>
+        <v>1393</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>1982</v>
+        <v>1946</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1166</v>
+        <v>1303</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>1982</v>
+        <v>1946</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1168</v>
+        <v>1314</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1120</v>
+        <v>1321</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1134</v>
+        <v>1328</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1143</v>
+        <v>1330</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1145</v>
+        <v>1337</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1150</v>
+        <v>1344</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1155</v>
+        <v>1346</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1162</v>
+        <v>1351</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1166</v>
+        <v>1360</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>1985</v>
+        <v>1946</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1168</v>
+        <v>1367</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1120</v>
+        <v>1369</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1134</v>
+        <v>1376</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1143</v>
+        <v>1383</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1145</v>
+        <v>1390</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1150</v>
+        <v>1393</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>1988</v>
+        <v>1949</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1155</v>
+        <v>1303</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>1988</v>
+        <v>1949</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1162</v>
+        <v>1314</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>1988</v>
+        <v>1949</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1166</v>
+        <v>1321</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>1988</v>
+        <v>1949</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1168</v>
+        <v>1328</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1504</v>
+        <v>1330</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1512</v>
+        <v>1337</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1519</v>
+        <v>1344</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1526</v>
+        <v>1346</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1535</v>
+        <v>1351</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1540</v>
+        <v>1360</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1303</v>
+        <v>1367</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1314</v>
+        <v>1369</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1321</v>
+        <v>1376</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>1328</v>
+        <v>1383</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1330</v>
+        <v>1390</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>1337</v>
+        <v>1393</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1344</v>
+        <v>1303</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>1346</v>
+        <v>1314</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1351</v>
+        <v>1321</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1360</v>
+        <v>1328</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1367</v>
+        <v>1330</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1369</v>
+        <v>1337</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1376</v>
+        <v>1344</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>1383</v>
+        <v>1346</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1390</v>
+        <v>1351</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>1990</v>
+        <v>1952</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1393</v>
+        <v>1360</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>2120</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1545</v>
+        <v>1367</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1554</v>
+        <v>1369</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1557</v>
+        <v>1376</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>1999</v>
+        <v>1952</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1545</v>
+        <v>1383</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>1999</v>
+        <v>1952</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1554</v>
+        <v>1390</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>1999</v>
+        <v>1952</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1557</v>
+        <v>1393</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>2001</v>
+        <v>1961</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1545</v>
+        <v>1504</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>2001</v>
+        <v>1961</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1554</v>
+        <v>1512</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>2001</v>
+        <v>1961</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>1557</v>
+        <v>1519</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>2004</v>
+        <v>1961</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1545</v>
+        <v>1526</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>2004</v>
+        <v>1961</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1554</v>
+        <v>1535</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>2004</v>
+        <v>1961</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1557</v>
+        <v>1540</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>2007</v>
+        <v>1964</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1545</v>
+        <v>1504</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>2007</v>
+        <v>1964</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1554</v>
+        <v>1512</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>2007</v>
+        <v>1964</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1557</v>
+        <v>1519</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>2010</v>
+        <v>1964</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1545</v>
+        <v>1526</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>2010</v>
+        <v>1964</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1554</v>
+        <v>1535</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>2010</v>
+        <v>1964</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1557</v>
+        <v>1540</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>2013</v>
+        <v>1967</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1545</v>
+        <v>1504</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>2013</v>
+        <v>1967</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1554</v>
+        <v>1512</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>2013</v>
+        <v>1967</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1557</v>
+        <v>1519</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>2016</v>
+        <v>1967</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1545</v>
+        <v>1526</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>2016</v>
+        <v>1967</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1554</v>
+        <v>1535</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>2016</v>
+        <v>1967</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1557</v>
+        <v>1540</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>2019</v>
+        <v>1970</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1545</v>
+        <v>1504</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>2019</v>
+        <v>1970</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1554</v>
+        <v>1512</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>2019</v>
+        <v>1970</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1557</v>
+        <v>1540</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>2022</v>
+        <v>1984</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1545</v>
+        <v>1120</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>2022</v>
+        <v>1984</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1554</v>
+        <v>1134</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>2022</v>
+        <v>1984</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1557</v>
+        <v>1143</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>2025</v>
+        <v>1984</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1545</v>
+        <v>1145</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>2025</v>
+        <v>1984</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1554</v>
+        <v>1150</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>2025</v>
+        <v>1984</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1557</v>
+        <v>1155</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>2028</v>
+        <v>1984</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1545</v>
+        <v>1162</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>2028</v>
+        <v>1984</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1554</v>
+        <v>1166</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>2028</v>
+        <v>1984</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1557</v>
+        <v>1168</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>2031</v>
+        <v>1981</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1545</v>
+        <v>1120</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>2031</v>
+        <v>1981</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1554</v>
+        <v>1134</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>2031</v>
+        <v>1981</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1557</v>
+        <v>1143</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>2034</v>
+        <v>1981</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1545</v>
+        <v>1150</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>2034</v>
+        <v>1981</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1554</v>
+        <v>1155</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>2034</v>
+        <v>1981</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1557</v>
+        <v>1162</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>2037</v>
+        <v>1981</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1545</v>
+        <v>1166</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>2037</v>
+        <v>1975</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1554</v>
+        <v>1145</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>2037</v>
+        <v>1975</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1557</v>
+        <v>1168</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>2040</v>
+        <v>1978</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1545</v>
+        <v>1145</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>2040</v>
+        <v>1978</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1554</v>
+        <v>1168</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="1" t="s">
-        <v>2040</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1557</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
-        <v>2046</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="1" t="s">
-        <v>2049</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="1" t="s">
-        <v>2052</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="1" t="s">
-        <v>2055</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="1" t="s">
-        <v>2055</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
-        <v>2058</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="1" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" s="1" t="s">
-        <v>2064</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
-        <v>2064</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
-        <v>2067</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="1" t="s">
-        <v>2067</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>1613</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" s="1" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>1613</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A346" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" s="1" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>1613</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C357" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" s="1" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B359" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" s="1" t="s">
-        <v>2080</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" s="1" t="s">
-        <v>2083</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C361" s="1" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C362" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C363" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A364" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B364" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B365" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C365" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A366" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B366" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C366" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" s="1" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A368" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C368" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A369" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B369" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C369" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A370" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B370" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C370" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A371" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B371" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C371" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A372" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B372" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B373" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C373" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B374" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C375" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B376" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C376" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B377" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C377" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" s="1" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B379" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C379" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A380" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B380" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A381" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C381" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C383" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B384" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C384" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B385" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C385" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B386" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B387" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B388" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B389" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B390" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B391" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A392" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B392" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B393" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C393" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B394" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B395" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C395" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B396" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B397" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B398" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B399" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B400" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B401" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B402" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B403" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B404" s="1" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A405" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B405" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C405" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B406" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B407" s="1" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B408" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B409" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C409" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" s="1" t="s">
-        <v>2110</v>
-      </c>
-      <c r="B410" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C410" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="1" t="s">
-        <v>2110</v>
-      </c>
-      <c r="B411" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="1" t="s">
-        <v>2113</v>
-      </c>
-      <c r="B412" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C412" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" s="1" t="s">
-        <v>2113</v>
-      </c>
-      <c r="B413" s="1" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
   </sheetData>
@@ -51309,10 +50325,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -51329,10 +50345,10 @@
         <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -51349,10 +50365,10 @@
         <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -51369,10 +50385,10 @@
         <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -51389,10 +50405,10 @@
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -51409,10 +50425,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -51429,10 +50445,10 @@
         <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -51449,10 +50465,10 @@
         <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -51469,10 +50485,10 @@
         <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -51489,10 +50505,10 @@
         <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -51509,10 +50525,10 @@
         <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -51529,10 +50545,10 @@
         <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -51549,10 +50565,10 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -51569,10 +50585,10 @@
         <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -51621,10 +50637,10 @@
         <v>28</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -51705,10 +50721,10 @@
         <v>28</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -51821,10 +50837,10 @@
         <v>28</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -51841,10 +50857,10 @@
         <v>28</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -51861,10 +50877,10 @@
         <v>28</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -51881,10 +50897,10 @@
         <v>28</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -51901,10 +50917,10 @@
         <v>28</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -51921,10 +50937,10 @@
         <v>28</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
   </sheetData>
